--- a/research/traditional_assets/database/data/latvia/latvia_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_beverage_alcoholic.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08678657186807702</v>
+        <v>0.08664899872434086</v>
       </c>
       <c r="C2">
-        <v>71.59151094434633</v>
+        <v>71.11477765506997</v>
       </c>
       <c r="D2">
-        <v>71.51951094434632</v>
+        <v>71.76037765506997</v>
       </c>
       <c r="E2">
-        <v>-2.26</v>
+        <v>-1.5424</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7176</v>
       </c>
       <c r="G2">
         <v>0.07199999999999999</v>
@@ -1445,28 +1445,28 @@
         <v>5.04</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03609528</v>
       </c>
       <c r="N2">
-        <v>5.04</v>
+        <v>5.00390472</v>
       </c>
       <c r="O2">
-        <v>1.008</v>
+        <v>1.000780944</v>
       </c>
       <c r="P2">
-        <v>4.032</v>
+        <v>4.003123776000001</v>
       </c>
       <c r="Q2">
-        <v>6.212</v>
+        <v>6.183123776</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08678657186807702</v>
+        <v>0.08711777648923319</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6966770696190074</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>139.6304447562119</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08664899872434086</v>
+        <v>0.08651142558060469</v>
       </c>
       <c r="C3">
-        <v>71.11477765506997</v>
+        <v>70.63967225232145</v>
       </c>
       <c r="D3">
-        <v>71.76037765506997</v>
+        <v>72.00287225232144</v>
       </c>
       <c r="E3">
-        <v>-1.5424</v>
+        <v>-0.8247999999999998</v>
       </c>
       <c r="F3">
-        <v>0.7176</v>
+        <v>1.4352</v>
       </c>
       <c r="G3">
         <v>0.07199999999999999</v>
@@ -1527,28 +1527,28 @@
         <v>5.04</v>
       </c>
       <c r="M3">
-        <v>0.03609528</v>
+        <v>0.07219056</v>
       </c>
       <c r="N3">
-        <v>5.00390472</v>
+        <v>4.96780944</v>
       </c>
       <c r="O3">
-        <v>1.000780944</v>
+        <v>0.993561888</v>
       </c>
       <c r="P3">
-        <v>4.003123776000001</v>
+        <v>3.974247552</v>
       </c>
       <c r="Q3">
-        <v>6.183123776</v>
+        <v>6.154247551999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08711777648923319</v>
+        <v>0.08745574038837214</v>
       </c>
       <c r="T3">
-        <v>0.6966770696190074</v>
+        <v>0.7023756264847307</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>139.6304447562119</v>
+        <v>69.81522237810594</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08651142558060469</v>
+        <v>0.08637385243686854</v>
       </c>
       <c r="C4">
-        <v>70.63967225232145</v>
+        <v>70.16621129505094</v>
       </c>
       <c r="D4">
-        <v>72.00287225232144</v>
+        <v>72.24701129505094</v>
       </c>
       <c r="E4">
-        <v>-0.8247999999999998</v>
+        <v>-0.1071999999999997</v>
       </c>
       <c r="F4">
-        <v>1.4352</v>
+        <v>2.1528</v>
       </c>
       <c r="G4">
         <v>0.07199999999999999</v>
@@ -1609,28 +1609,28 @@
         <v>5.04</v>
       </c>
       <c r="M4">
-        <v>0.07219056</v>
+        <v>0.10828584</v>
       </c>
       <c r="N4">
-        <v>4.96780944</v>
+        <v>4.93171416</v>
       </c>
       <c r="O4">
-        <v>0.993561888</v>
+        <v>0.9863428320000001</v>
       </c>
       <c r="P4">
-        <v>3.974247552</v>
+        <v>3.945371328</v>
       </c>
       <c r="Q4">
-        <v>6.154247551999999</v>
+        <v>6.125371328</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08745574038837214</v>
+        <v>0.0878006726153284</v>
       </c>
       <c r="T4">
-        <v>0.7023756264847307</v>
+        <v>0.708191679368304</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.81522237810594</v>
+        <v>46.54348158540397</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08637385243686854</v>
+        <v>0.08623627929313241</v>
       </c>
       <c r="C5">
-        <v>70.16621129505094</v>
+        <v>69.69441156755741</v>
       </c>
       <c r="D5">
-        <v>72.24701129505094</v>
+        <v>72.49281156755741</v>
       </c>
       <c r="E5">
-        <v>-0.1071999999999997</v>
+        <v>0.6104000000000003</v>
       </c>
       <c r="F5">
-        <v>2.1528</v>
+        <v>2.8704</v>
       </c>
       <c r="G5">
         <v>0.07199999999999999</v>
@@ -1691,28 +1691,28 @@
         <v>5.04</v>
       </c>
       <c r="M5">
-        <v>0.10828584</v>
+        <v>0.14438112</v>
       </c>
       <c r="N5">
-        <v>4.93171416</v>
+        <v>4.89561888</v>
       </c>
       <c r="O5">
-        <v>0.9863428320000001</v>
+        <v>0.979123776</v>
       </c>
       <c r="P5">
-        <v>3.945371328</v>
+        <v>3.916495104</v>
       </c>
       <c r="Q5">
-        <v>6.125371328</v>
+        <v>6.096495104</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0878006726153284</v>
+        <v>0.08815279093034625</v>
       </c>
       <c r="T5">
-        <v>0.708191679368304</v>
+        <v>0.7141289000202852</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.54348158540397</v>
+        <v>34.90761118905297</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08623627929313241</v>
+        <v>0.08609870614939624</v>
       </c>
       <c r="C6">
-        <v>69.69441156755741</v>
+        <v>69.22429008333533</v>
       </c>
       <c r="D6">
-        <v>72.49281156755741</v>
+        <v>72.74029008333532</v>
       </c>
       <c r="E6">
-        <v>0.6104000000000003</v>
+        <v>1.328000000000001</v>
       </c>
       <c r="F6">
-        <v>2.8704</v>
+        <v>3.588000000000001</v>
       </c>
       <c r="G6">
         <v>0.07199999999999999</v>
@@ -1773,28 +1773,28 @@
         <v>5.04</v>
       </c>
       <c r="M6">
-        <v>0.14438112</v>
+        <v>0.1804764</v>
       </c>
       <c r="N6">
-        <v>4.89561888</v>
+        <v>4.8595236</v>
       </c>
       <c r="O6">
-        <v>0.979123776</v>
+        <v>0.9719047200000001</v>
       </c>
       <c r="P6">
-        <v>3.916495104</v>
+        <v>3.88761888</v>
       </c>
       <c r="Q6">
-        <v>6.096495104</v>
+        <v>6.067618879999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08815279093034625</v>
+        <v>0.08851232226252237</v>
       </c>
       <c r="T6">
-        <v>0.7141289000202852</v>
+        <v>0.7201911147912552</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.90761118905297</v>
+        <v>27.92608895124238</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08609870614939624</v>
+        <v>0.08596113300566009</v>
       </c>
       <c r="C7">
-        <v>69.22429008333533</v>
+        <v>68.7558640889998</v>
       </c>
       <c r="D7">
-        <v>72.74029008333532</v>
+        <v>72.9894640889998</v>
       </c>
       <c r="E7">
-        <v>1.328000000000001</v>
+        <v>2.045600000000001</v>
       </c>
       <c r="F7">
-        <v>3.588000000000001</v>
+        <v>4.305600000000001</v>
       </c>
       <c r="G7">
         <v>0.07199999999999999</v>
@@ -1855,28 +1855,28 @@
         <v>5.04</v>
       </c>
       <c r="M7">
-        <v>0.1804764</v>
+        <v>0.21657168</v>
       </c>
       <c r="N7">
-        <v>4.8595236</v>
+        <v>4.82342832</v>
       </c>
       <c r="O7">
-        <v>0.9719047200000001</v>
+        <v>0.964685664</v>
       </c>
       <c r="P7">
-        <v>3.88761888</v>
+        <v>3.858742656</v>
       </c>
       <c r="Q7">
-        <v>6.067618879999999</v>
+        <v>6.038742655999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08851232226252237</v>
+        <v>0.08887950319751074</v>
       </c>
       <c r="T7">
-        <v>0.7201911147912552</v>
+        <v>0.7263823128552249</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.92608895124238</v>
+        <v>23.27174079270198</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08596113300566009</v>
+        <v>0.08582355986192394</v>
       </c>
       <c r="C8">
-        <v>68.7558640889998</v>
+        <v>68.28915106829353</v>
       </c>
       <c r="D8">
-        <v>72.9894640889998</v>
+        <v>73.24035106829353</v>
       </c>
       <c r="E8">
-        <v>2.0456</v>
+        <v>2.7632</v>
       </c>
       <c r="F8">
-        <v>4.3056</v>
+        <v>5.0232</v>
       </c>
       <c r="G8">
         <v>0.07199999999999999</v>
@@ -1937,28 +1937,28 @@
         <v>5.04</v>
       </c>
       <c r="M8">
-        <v>0.21657168</v>
+        <v>0.25266696</v>
       </c>
       <c r="N8">
-        <v>4.82342832</v>
+        <v>4.78733304</v>
       </c>
       <c r="O8">
-        <v>0.964685664</v>
+        <v>0.9574666080000001</v>
       </c>
       <c r="P8">
-        <v>3.858742656</v>
+        <v>3.829866432</v>
       </c>
       <c r="Q8">
-        <v>6.038742655999999</v>
+        <v>6.009866432</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08887950319751074</v>
+        <v>0.08925458049669241</v>
       </c>
       <c r="T8">
-        <v>0.7263823128552249</v>
+        <v>0.7327066549635809</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.27174079270198</v>
+        <v>19.94720639374456</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08582355986192393</v>
+        <v>0.08568598671818781</v>
       </c>
       <c r="C9">
-        <v>68.28915106829355</v>
+        <v>67.8241687461761</v>
       </c>
       <c r="D9">
-        <v>73.24035106829355</v>
+        <v>73.4929687461761</v>
       </c>
       <c r="E9">
-        <v>2.763200000000001</v>
+        <v>3.4808</v>
       </c>
       <c r="F9">
-        <v>5.023200000000001</v>
+        <v>5.7408</v>
       </c>
       <c r="G9">
         <v>0.07199999999999999</v>
@@ -2019,28 +2019,28 @@
         <v>5.04</v>
       </c>
       <c r="M9">
-        <v>0.2526669600000001</v>
+        <v>0.28876224</v>
       </c>
       <c r="N9">
-        <v>4.78733304</v>
+        <v>4.75123776</v>
       </c>
       <c r="O9">
-        <v>0.9574666080000001</v>
+        <v>0.9502475520000001</v>
       </c>
       <c r="P9">
-        <v>3.829866432</v>
+        <v>3.800990208</v>
       </c>
       <c r="Q9">
-        <v>6.009866432</v>
+        <v>5.980990208</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08925458049669241</v>
+        <v>0.08963781165020412</v>
       </c>
       <c r="T9">
-        <v>0.7327066549635809</v>
+        <v>0.7391684827699445</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.94720639374455</v>
+        <v>17.45380559452649</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08568598671818781</v>
+        <v>0.08554841357445164</v>
       </c>
       <c r="C10">
-        <v>67.8241687461761</v>
+        <v>67.36093509299839</v>
       </c>
       <c r="D10">
-        <v>73.4929687461761</v>
+        <v>73.74733509299838</v>
       </c>
       <c r="E10">
-        <v>3.4808</v>
+        <v>4.1984</v>
       </c>
       <c r="F10">
-        <v>5.7408</v>
+        <v>6.4584</v>
       </c>
       <c r="G10">
         <v>0.07199999999999999</v>
@@ -2101,28 +2101,28 @@
         <v>5.04</v>
       </c>
       <c r="M10">
-        <v>0.28876224</v>
+        <v>0.32485752</v>
       </c>
       <c r="N10">
-        <v>4.75123776</v>
+        <v>4.71514248</v>
       </c>
       <c r="O10">
-        <v>0.9502475520000001</v>
+        <v>0.943028496</v>
       </c>
       <c r="P10">
-        <v>3.800990208</v>
+        <v>3.772113984</v>
       </c>
       <c r="Q10">
-        <v>5.980990208</v>
+        <v>5.952113983999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08963781165020412</v>
+        <v>0.09002946546643037</v>
       </c>
       <c r="T10">
-        <v>0.7391684827699445</v>
+        <v>0.7457723287698547</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.45380559452649</v>
+        <v>15.51449386180132</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08554841357445164</v>
+        <v>0.08541084043071548</v>
       </c>
       <c r="C11">
-        <v>67.36093509299839</v>
+        <v>66.89946832876385</v>
       </c>
       <c r="D11">
-        <v>73.74733509299838</v>
+        <v>74.00346832876384</v>
       </c>
       <c r="E11">
-        <v>4.1984</v>
+        <v>4.916</v>
       </c>
       <c r="F11">
-        <v>6.4584</v>
+        <v>7.176</v>
       </c>
       <c r="G11">
         <v>0.07199999999999999</v>
@@ -2183,28 +2183,28 @@
         <v>5.04</v>
       </c>
       <c r="M11">
-        <v>0.32485752</v>
+        <v>0.3609528</v>
       </c>
       <c r="N11">
-        <v>4.71514248</v>
+        <v>4.6790472</v>
       </c>
       <c r="O11">
-        <v>0.943028496</v>
+        <v>0.9358094400000001</v>
       </c>
       <c r="P11">
-        <v>3.772113984</v>
+        <v>3.74323776</v>
       </c>
       <c r="Q11">
-        <v>5.952113983999999</v>
+        <v>5.92323776</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09002946546643037</v>
+        <v>0.09042982270079497</v>
       </c>
       <c r="T11">
-        <v>0.7457723287698547</v>
+        <v>0.7525229269030961</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.51449386180132</v>
+        <v>13.96304447562119</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08541084043071549</v>
+        <v>0.08540526728697932</v>
       </c>
       <c r="C12">
-        <v>66.89946832876382</v>
+        <v>66.19228189226745</v>
       </c>
       <c r="D12">
-        <v>74.00346832876382</v>
+        <v>74.01388189226745</v>
       </c>
       <c r="E12">
-        <v>4.916000000000001</v>
+        <v>5.6336</v>
       </c>
       <c r="F12">
-        <v>7.176000000000001</v>
+        <v>7.8936</v>
       </c>
       <c r="G12">
         <v>0.07199999999999999</v>
@@ -2265,45 +2265,45 @@
         <v>5.04</v>
       </c>
       <c r="M12">
-        <v>0.3609528</v>
+        <v>0.40888848</v>
       </c>
       <c r="N12">
-        <v>4.6790472</v>
+        <v>4.63111152</v>
       </c>
       <c r="O12">
-        <v>0.9358094400000001</v>
+        <v>0.9262223040000001</v>
       </c>
       <c r="P12">
-        <v>3.74323776</v>
+        <v>3.704889216</v>
       </c>
       <c r="Q12">
-        <v>5.92323776</v>
+        <v>5.884889215999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09042982270079498</v>
+        <v>0.09083917672694306</v>
       </c>
       <c r="T12">
-        <v>0.7525229269030963</v>
+        <v>0.7594252238707925</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.96304447562119</v>
+        <v>12.32609928262102</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08540526728697932</v>
+        <v>0.08527969414324317</v>
       </c>
       <c r="C13">
-        <v>66.19228189226745</v>
+        <v>65.71009799745831</v>
       </c>
       <c r="D13">
-        <v>74.01388189226745</v>
+        <v>74.2492979974583</v>
       </c>
       <c r="E13">
-        <v>5.6336</v>
+        <v>6.3512</v>
       </c>
       <c r="F13">
-        <v>7.8936</v>
+        <v>8.6112</v>
       </c>
       <c r="G13">
         <v>0.07199999999999999</v>
@@ -2347,28 +2347,28 @@
         <v>5.04</v>
       </c>
       <c r="M13">
-        <v>0.40888848</v>
+        <v>0.44606016</v>
       </c>
       <c r="N13">
-        <v>4.63111152</v>
+        <v>4.59393984</v>
       </c>
       <c r="O13">
-        <v>0.9262223040000001</v>
+        <v>0.9187879680000001</v>
       </c>
       <c r="P13">
-        <v>3.704889216</v>
+        <v>3.675151872</v>
       </c>
       <c r="Q13">
-        <v>5.884889215999999</v>
+        <v>5.855151872</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09083917672694306</v>
+        <v>0.09125783425368542</v>
       </c>
       <c r="T13">
-        <v>0.7594252238707925</v>
+        <v>0.7664843912241184</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.32609928262102</v>
+        <v>11.2989243424026</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08527969414324317</v>
+        <v>0.08515412099950702</v>
       </c>
       <c r="C14">
-        <v>65.71009799745831</v>
+        <v>65.2294164581669</v>
       </c>
       <c r="D14">
-        <v>74.2492979974583</v>
+        <v>74.48621645816689</v>
       </c>
       <c r="E14">
-        <v>6.3512</v>
+        <v>7.068800000000001</v>
       </c>
       <c r="F14">
-        <v>8.6112</v>
+        <v>9.328800000000001</v>
       </c>
       <c r="G14">
         <v>0.07199999999999999</v>
@@ -2429,28 +2429,28 @@
         <v>5.04</v>
       </c>
       <c r="M14">
-        <v>0.44606016</v>
+        <v>0.48323184</v>
       </c>
       <c r="N14">
-        <v>4.59393984</v>
+        <v>4.55676816</v>
       </c>
       <c r="O14">
-        <v>0.9187879680000001</v>
+        <v>0.911353632</v>
       </c>
       <c r="P14">
-        <v>3.675151872</v>
+        <v>3.645414528</v>
       </c>
       <c r="Q14">
-        <v>5.855151872</v>
+        <v>5.825414528</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09125783425368542</v>
+        <v>0.09168611609138738</v>
       </c>
       <c r="T14">
-        <v>0.7664843912241184</v>
+        <v>0.773705838286716</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.2989243424026</v>
+        <v>10.42977631606394</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08515412099950702</v>
+        <v>0.08521894785577086</v>
       </c>
       <c r="C15">
-        <v>65.2294164581669</v>
+        <v>64.38931934673614</v>
       </c>
       <c r="D15">
-        <v>74.48621645816689</v>
+        <v>74.36371934673615</v>
       </c>
       <c r="E15">
-        <v>7.068800000000001</v>
+        <v>7.786400000000002</v>
       </c>
       <c r="F15">
-        <v>9.328800000000001</v>
+        <v>10.0464</v>
       </c>
       <c r="G15">
         <v>0.07199999999999999</v>
@@ -2511,45 +2511,45 @@
         <v>5.04</v>
       </c>
       <c r="M15">
-        <v>0.48323184</v>
+        <v>0.5374824000000001</v>
       </c>
       <c r="N15">
-        <v>4.55676816</v>
+        <v>4.5025176</v>
       </c>
       <c r="O15">
-        <v>0.911353632</v>
+        <v>0.90050352</v>
       </c>
       <c r="P15">
-        <v>3.645414528</v>
+        <v>3.60201408</v>
       </c>
       <c r="Q15">
-        <v>5.825414528</v>
+        <v>5.78201408</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09168611609138738</v>
+        <v>0.09212435797182658</v>
       </c>
       <c r="T15">
-        <v>0.773705838286716</v>
+        <v>0.7810952259786765</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.42977631606394</v>
+        <v>9.377051229956551</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08521894785577086</v>
+        <v>0.0851069747120347</v>
       </c>
       <c r="C16">
-        <v>64.38931934673614</v>
+        <v>63.88355807246283</v>
       </c>
       <c r="D16">
-        <v>74.36371934673615</v>
+        <v>74.57555807246283</v>
       </c>
       <c r="E16">
-        <v>7.786400000000002</v>
+        <v>8.504000000000003</v>
       </c>
       <c r="F16">
-        <v>10.0464</v>
+        <v>10.764</v>
       </c>
       <c r="G16">
         <v>0.07199999999999999</v>
@@ -2593,28 +2593,28 @@
         <v>5.04</v>
       </c>
       <c r="M16">
-        <v>0.5374824000000001</v>
+        <v>0.5758740000000001</v>
       </c>
       <c r="N16">
-        <v>4.5025176</v>
+        <v>4.464126</v>
       </c>
       <c r="O16">
-        <v>0.90050352</v>
+        <v>0.8928252000000001</v>
       </c>
       <c r="P16">
-        <v>3.60201408</v>
+        <v>3.5713008</v>
       </c>
       <c r="Q16">
-        <v>5.78201408</v>
+        <v>5.7513008</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09212435797182658</v>
+        <v>0.09257291142592318</v>
       </c>
       <c r="T16">
-        <v>0.7810952259786765</v>
+        <v>0.78865848161633</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.377051229956551</v>
+        <v>8.751914481292783</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0851069747120347</v>
+        <v>0.08499500156829855</v>
       </c>
       <c r="C17">
-        <v>63.88355807246283</v>
+        <v>63.37900716926411</v>
       </c>
       <c r="D17">
-        <v>74.57555807246283</v>
+        <v>74.78860716926411</v>
       </c>
       <c r="E17">
-        <v>8.504000000000001</v>
+        <v>9.2216</v>
       </c>
       <c r="F17">
-        <v>10.764</v>
+        <v>11.4816</v>
       </c>
       <c r="G17">
         <v>0.07199999999999999</v>
@@ -2675,28 +2675,28 @@
         <v>5.04</v>
       </c>
       <c r="M17">
-        <v>0.575874</v>
+        <v>0.6142656</v>
       </c>
       <c r="N17">
-        <v>4.464126</v>
+        <v>4.4257344</v>
       </c>
       <c r="O17">
-        <v>0.8928252000000001</v>
+        <v>0.88514688</v>
       </c>
       <c r="P17">
-        <v>3.5713008</v>
+        <v>3.54058752</v>
       </c>
       <c r="Q17">
-        <v>5.7513008</v>
+        <v>5.72058752</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09257291142592318</v>
+        <v>0.09303214472416493</v>
       </c>
       <c r="T17">
-        <v>0.78865848161633</v>
+        <v>0.7964018147691658</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.751914481292783</v>
+        <v>8.204919826211984</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08499500156829855</v>
+        <v>0.0848830284245624</v>
       </c>
       <c r="C18">
-        <v>63.37900716926411</v>
+        <v>62.87567704030428</v>
       </c>
       <c r="D18">
-        <v>74.78860716926411</v>
+        <v>75.00287704030428</v>
       </c>
       <c r="E18">
-        <v>9.2216</v>
+        <v>9.939200000000001</v>
       </c>
       <c r="F18">
-        <v>11.4816</v>
+        <v>12.1992</v>
       </c>
       <c r="G18">
         <v>0.07199999999999999</v>
@@ -2757,28 +2757,28 @@
         <v>5.04</v>
       </c>
       <c r="M18">
-        <v>0.6142656</v>
+        <v>0.6526572</v>
       </c>
       <c r="N18">
-        <v>4.4257344</v>
+        <v>4.3873428</v>
       </c>
       <c r="O18">
-        <v>0.88514688</v>
+        <v>0.8774685600000001</v>
       </c>
       <c r="P18">
-        <v>3.54058752</v>
+        <v>3.50987424</v>
       </c>
       <c r="Q18">
-        <v>5.72058752</v>
+        <v>5.68987424</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09303214472416493</v>
+        <v>0.09350244388501494</v>
       </c>
       <c r="T18">
-        <v>0.7964018147691658</v>
+        <v>0.8043317342630339</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.204919826211984</v>
+        <v>7.722277483493631</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0848830284245624</v>
+        <v>0.08488625528082624</v>
       </c>
       <c r="C19">
-        <v>62.87567704030428</v>
+        <v>62.15188500420759</v>
       </c>
       <c r="D19">
-        <v>75.00287704030428</v>
+        <v>74.99668500420759</v>
       </c>
       <c r="E19">
-        <v>9.939200000000001</v>
+        <v>10.6568</v>
       </c>
       <c r="F19">
-        <v>12.1992</v>
+        <v>12.9168</v>
       </c>
       <c r="G19">
         <v>0.07199999999999999</v>
@@ -2839,45 +2839,45 @@
         <v>5.04</v>
       </c>
       <c r="M19">
-        <v>0.6526572</v>
+        <v>0.7013822400000002</v>
       </c>
       <c r="N19">
-        <v>4.3873428</v>
+        <v>4.33861776</v>
       </c>
       <c r="O19">
-        <v>0.8774685600000001</v>
+        <v>0.8677235520000001</v>
       </c>
       <c r="P19">
-        <v>3.50987424</v>
+        <v>3.470894208</v>
       </c>
       <c r="Q19">
-        <v>5.68987424</v>
+        <v>5.650894208</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09350244388501494</v>
+        <v>0.09398421375710518</v>
       </c>
       <c r="T19">
-        <v>0.8043317342630339</v>
+        <v>0.8124550664274842</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.722277483493631</v>
+        <v>7.185810692896927</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08488625528082624</v>
+        <v>0.0847806821370901</v>
       </c>
       <c r="C20">
-        <v>62.15188500420759</v>
+        <v>61.6374019167808</v>
       </c>
       <c r="D20">
-        <v>74.99668500420759</v>
+        <v>75.1998019167808</v>
       </c>
       <c r="E20">
-        <v>10.6568</v>
+        <v>11.3744</v>
       </c>
       <c r="F20">
-        <v>12.9168</v>
+        <v>13.6344</v>
       </c>
       <c r="G20">
         <v>0.07199999999999999</v>
@@ -2921,28 +2921,28 @@
         <v>5.04</v>
       </c>
       <c r="M20">
-        <v>0.70138224</v>
+        <v>0.74034792</v>
       </c>
       <c r="N20">
-        <v>4.33861776</v>
+        <v>4.29965208</v>
       </c>
       <c r="O20">
-        <v>0.8677235520000001</v>
+        <v>0.859930416</v>
       </c>
       <c r="P20">
-        <v>3.470894208</v>
+        <v>3.439721663999999</v>
       </c>
       <c r="Q20">
-        <v>5.650894208</v>
+        <v>5.619721663999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09398421375710517</v>
+        <v>0.09447787918159271</v>
       </c>
       <c r="T20">
-        <v>0.8124550664274841</v>
+        <v>0.8207789746947604</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.185810692896928</v>
+        <v>6.807610130112879</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0847806821370901</v>
+        <v>0.08467510899335394</v>
       </c>
       <c r="C21">
-        <v>61.6374019167808</v>
+        <v>61.12402203866003</v>
       </c>
       <c r="D21">
-        <v>75.1998019167808</v>
+        <v>75.40402203866003</v>
       </c>
       <c r="E21">
-        <v>11.3744</v>
+        <v>12.092</v>
       </c>
       <c r="F21">
-        <v>13.6344</v>
+        <v>14.352</v>
       </c>
       <c r="G21">
         <v>0.07199999999999999</v>
@@ -3003,28 +3003,28 @@
         <v>5.04</v>
       </c>
       <c r="M21">
-        <v>0.74034792</v>
+        <v>0.7793136000000002</v>
       </c>
       <c r="N21">
-        <v>4.29965208</v>
+        <v>4.2606864</v>
       </c>
       <c r="O21">
-        <v>0.859930416</v>
+        <v>0.85213728</v>
       </c>
       <c r="P21">
-        <v>3.439721663999999</v>
+        <v>3.40854912</v>
       </c>
       <c r="Q21">
-        <v>5.619721663999999</v>
+        <v>5.58854912</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09447787918159271</v>
+        <v>0.09498388624169242</v>
       </c>
       <c r="T21">
-        <v>0.8207789746947604</v>
+        <v>0.8293109806687182</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.807610130112879</v>
+        <v>6.467229623607235</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08467510899335394</v>
+        <v>0.08456953584961779</v>
       </c>
       <c r="C22">
-        <v>61.12402203866003</v>
+        <v>60.61175438227769</v>
       </c>
       <c r="D22">
-        <v>75.40402203866003</v>
+        <v>75.60935438227769</v>
       </c>
       <c r="E22">
-        <v>12.092</v>
+        <v>12.8096</v>
       </c>
       <c r="F22">
-        <v>14.352</v>
+        <v>15.0696</v>
       </c>
       <c r="G22">
         <v>0.07199999999999999</v>
@@ -3085,28 +3085,28 @@
         <v>5.04</v>
       </c>
       <c r="M22">
-        <v>0.7793136000000002</v>
+        <v>0.8182792800000002</v>
       </c>
       <c r="N22">
-        <v>4.2606864</v>
+        <v>4.22172072</v>
       </c>
       <c r="O22">
-        <v>0.85213728</v>
+        <v>0.8443441439999999</v>
       </c>
       <c r="P22">
-        <v>3.40854912</v>
+        <v>3.377376576</v>
       </c>
       <c r="Q22">
-        <v>5.58854912</v>
+        <v>5.557376575999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09498388624169242</v>
+        <v>0.09550270360711112</v>
       </c>
       <c r="T22">
-        <v>0.8293109806687182</v>
+        <v>0.8380589867939157</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.467229623607235</v>
+        <v>6.159266308197366</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08456953584961779</v>
+        <v>0.08463996270588163</v>
       </c>
       <c r="C23">
-        <v>60.61175438227769</v>
+        <v>59.75705514833648</v>
       </c>
       <c r="D23">
-        <v>75.60935438227769</v>
+        <v>75.47225514833647</v>
       </c>
       <c r="E23">
-        <v>12.8096</v>
+        <v>13.5272</v>
       </c>
       <c r="F23">
-        <v>15.0696</v>
+        <v>15.7872</v>
       </c>
       <c r="G23">
         <v>0.07199999999999999</v>
@@ -3167,45 +3167,45 @@
         <v>5.04</v>
       </c>
       <c r="M23">
-        <v>0.8182792800000001</v>
+        <v>0.8730321600000001</v>
       </c>
       <c r="N23">
-        <v>4.22172072</v>
+        <v>4.16696784</v>
       </c>
       <c r="O23">
-        <v>0.8443441440000001</v>
+        <v>0.833393568</v>
       </c>
       <c r="P23">
-        <v>3.377376576000001</v>
+        <v>3.333574272</v>
       </c>
       <c r="Q23">
-        <v>5.557376576</v>
+        <v>5.513574272</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09550270360711112</v>
+        <v>0.09603482398189953</v>
       </c>
       <c r="T23">
-        <v>0.8380589867939157</v>
+        <v>0.8470313007684772</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.159266308197368</v>
+        <v>5.772983208316174</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08463996270588163</v>
+        <v>0.08454238956214548</v>
       </c>
       <c r="C24">
-        <v>59.75705514833648</v>
+        <v>59.22953287154627</v>
       </c>
       <c r="D24">
-        <v>75.47225514833647</v>
+        <v>75.66233287154627</v>
       </c>
       <c r="E24">
-        <v>13.5272</v>
+        <v>14.2448</v>
       </c>
       <c r="F24">
-        <v>15.7872</v>
+        <v>16.5048</v>
       </c>
       <c r="G24">
         <v>0.07199999999999999</v>
@@ -3249,28 +3249,28 @@
         <v>5.04</v>
       </c>
       <c r="M24">
-        <v>0.8730321600000001</v>
+        <v>0.9127154400000002</v>
       </c>
       <c r="N24">
-        <v>4.16696784</v>
+        <v>4.12728456</v>
       </c>
       <c r="O24">
-        <v>0.833393568</v>
+        <v>0.8254569119999999</v>
       </c>
       <c r="P24">
-        <v>3.333574272</v>
+        <v>3.301827648</v>
       </c>
       <c r="Q24">
-        <v>5.513574272</v>
+        <v>5.481827647999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09603482398189953</v>
+        <v>0.096580765665124</v>
       </c>
       <c r="T24">
-        <v>0.8470313007684772</v>
+        <v>0.8562366618592611</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.772983208316174</v>
+        <v>5.521983938389384</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08454238956214548</v>
+        <v>0.08444481641840933</v>
       </c>
       <c r="C25">
-        <v>59.22953287154627</v>
+        <v>58.70297043789816</v>
       </c>
       <c r="D25">
-        <v>75.66233287154627</v>
+        <v>75.85337043789816</v>
       </c>
       <c r="E25">
-        <v>14.2448</v>
+        <v>14.9624</v>
       </c>
       <c r="F25">
-        <v>16.5048</v>
+        <v>17.2224</v>
       </c>
       <c r="G25">
         <v>0.07199999999999999</v>
@@ -3331,28 +3331,28 @@
         <v>5.04</v>
       </c>
       <c r="M25">
-        <v>0.9127154400000002</v>
+        <v>0.9523987200000003</v>
       </c>
       <c r="N25">
-        <v>4.12728456</v>
+        <v>4.087601279999999</v>
       </c>
       <c r="O25">
-        <v>0.8254569119999999</v>
+        <v>0.8175202559999999</v>
       </c>
       <c r="P25">
-        <v>3.301827648</v>
+        <v>3.270081024</v>
       </c>
       <c r="Q25">
-        <v>5.481827647999999</v>
+        <v>5.450081023999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.096580765665124</v>
+        <v>0.0971410742347491</v>
       </c>
       <c r="T25">
-        <v>0.8562366618592611</v>
+        <v>0.8656842692945392</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.521983938389384</v>
+        <v>5.291901274289825</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08444481641840933</v>
+        <v>0.08434724327467316</v>
       </c>
       <c r="C26">
-        <v>58.70297043789817</v>
+        <v>58.17737513623342</v>
       </c>
       <c r="D26">
-        <v>75.85337043789816</v>
+        <v>76.04537513623342</v>
       </c>
       <c r="E26">
-        <v>14.9624</v>
+        <v>15.68</v>
       </c>
       <c r="F26">
-        <v>17.2224</v>
+        <v>17.94</v>
       </c>
       <c r="G26">
         <v>0.07199999999999999</v>
@@ -3413,28 +3413,28 @@
         <v>5.04</v>
       </c>
       <c r="M26">
-        <v>0.95239872</v>
+        <v>0.9920820000000001</v>
       </c>
       <c r="N26">
-        <v>4.08760128</v>
+        <v>4.047918</v>
       </c>
       <c r="O26">
-        <v>0.8175202560000001</v>
+        <v>0.8095836000000001</v>
       </c>
       <c r="P26">
-        <v>3.270081024</v>
+        <v>3.2383344</v>
       </c>
       <c r="Q26">
-        <v>5.450081024</v>
+        <v>5.4183344</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0971410742347491</v>
+        <v>0.09771632436623089</v>
       </c>
       <c r="T26">
-        <v>0.8656842692945391</v>
+        <v>0.8753838129280914</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.291901274289827</v>
+        <v>5.080225223318234</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08434724327467316</v>
+        <v>0.08424967013093701</v>
       </c>
       <c r="C27">
-        <v>58.17737513623342</v>
+        <v>57.65275432938043</v>
       </c>
       <c r="D27">
-        <v>76.04537513623342</v>
+        <v>76.23835432938043</v>
       </c>
       <c r="E27">
-        <v>15.68</v>
+        <v>16.3976</v>
       </c>
       <c r="F27">
-        <v>17.94</v>
+        <v>18.6576</v>
       </c>
       <c r="G27">
         <v>0.07199999999999999</v>
@@ -3495,28 +3495,28 @@
         <v>5.04</v>
       </c>
       <c r="M27">
-        <v>0.9920820000000001</v>
+        <v>1.03176528</v>
       </c>
       <c r="N27">
-        <v>4.047918</v>
+        <v>4.00823472</v>
       </c>
       <c r="O27">
-        <v>0.8095836000000001</v>
+        <v>0.801646944</v>
       </c>
       <c r="P27">
-        <v>3.2383344</v>
+        <v>3.206587776</v>
       </c>
       <c r="Q27">
-        <v>5.4183344</v>
+        <v>5.386587776</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09771632436623089</v>
+        <v>0.09830712179856353</v>
       </c>
       <c r="T27">
-        <v>0.8753838129280914</v>
+        <v>0.8853455063895775</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.080225223318234</v>
+        <v>4.884831945498301</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08424967013093701</v>
+        <v>0.08415209698720087</v>
       </c>
       <c r="C28">
-        <v>57.65275432938043</v>
+        <v>57.12911545509593</v>
       </c>
       <c r="D28">
-        <v>76.23835432938043</v>
+        <v>76.43231545509593</v>
       </c>
       <c r="E28">
-        <v>16.3976</v>
+        <v>17.1152</v>
       </c>
       <c r="F28">
-        <v>18.6576</v>
+        <v>19.3752</v>
       </c>
       <c r="G28">
         <v>0.07199999999999999</v>
@@ -3577,28 +3577,28 @@
         <v>5.04</v>
       </c>
       <c r="M28">
-        <v>1.03176528</v>
+        <v>1.07144856</v>
       </c>
       <c r="N28">
-        <v>4.00823472</v>
+        <v>3.96855144</v>
       </c>
       <c r="O28">
-        <v>0.801646944</v>
+        <v>0.793710288</v>
       </c>
       <c r="P28">
-        <v>3.206587776</v>
+        <v>3.174841152</v>
       </c>
       <c r="Q28">
-        <v>5.386587776</v>
+        <v>5.354841152</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09830712179856353</v>
+        <v>0.09891410546191899</v>
       </c>
       <c r="T28">
-        <v>0.8853455063895775</v>
+        <v>0.8955801229595977</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.884831945498301</v>
+        <v>4.703912243813178</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08415209698720087</v>
+        <v>0.08405452384346471</v>
       </c>
       <c r="C29">
-        <v>57.12911545509593</v>
+        <v>56.60646602702057</v>
       </c>
       <c r="D29">
-        <v>76.43231545509593</v>
+        <v>76.62726602702057</v>
       </c>
       <c r="E29">
-        <v>17.1152</v>
+        <v>17.83280000000001</v>
       </c>
       <c r="F29">
-        <v>19.3752</v>
+        <v>20.0928</v>
       </c>
       <c r="G29">
         <v>0.07199999999999999</v>
@@ -3659,28 +3659,28 @@
         <v>5.04</v>
       </c>
       <c r="M29">
-        <v>1.07144856</v>
+        <v>1.11113184</v>
       </c>
       <c r="N29">
-        <v>3.96855144</v>
+        <v>3.928868159999999</v>
       </c>
       <c r="O29">
-        <v>0.793710288</v>
+        <v>0.7857736319999999</v>
       </c>
       <c r="P29">
-        <v>3.174841152</v>
+        <v>3.143094528</v>
       </c>
       <c r="Q29">
-        <v>5.354841152</v>
+        <v>5.323094527999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09891410546191899</v>
+        <v>0.09953794978258987</v>
       </c>
       <c r="T29">
-        <v>0.8955801229595977</v>
+        <v>0.9060990344343403</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.703912243813178</v>
+        <v>4.535915377962707</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08405452384346471</v>
+        <v>0.08453695069972857</v>
       </c>
       <c r="C30">
-        <v>56.60646602702057</v>
+        <v>54.93455624306101</v>
       </c>
       <c r="D30">
-        <v>76.62726602702057</v>
+        <v>75.67295624306101</v>
       </c>
       <c r="E30">
-        <v>17.83280000000001</v>
+        <v>18.5504</v>
       </c>
       <c r="F30">
-        <v>20.0928</v>
+        <v>20.8104</v>
       </c>
       <c r="G30">
         <v>0.07199999999999999</v>
@@ -3741,45 +3741,45 @@
         <v>5.04</v>
       </c>
       <c r="M30">
-        <v>1.11113184</v>
+        <v>1.20284112</v>
       </c>
       <c r="N30">
-        <v>3.928868159999999</v>
+        <v>3.83715888</v>
       </c>
       <c r="O30">
-        <v>0.7857736319999999</v>
+        <v>0.767431776</v>
       </c>
       <c r="P30">
-        <v>3.143094528</v>
+        <v>3.069727104</v>
       </c>
       <c r="Q30">
-        <v>5.323094527999999</v>
+        <v>5.249727104</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09953794978258987</v>
+        <v>0.1001793671827163</v>
       </c>
       <c r="T30">
-        <v>0.9060990344343403</v>
+        <v>0.9169142532745688</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.535915377962707</v>
+        <v>4.190079567615712</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08453695069972855</v>
+        <v>0.08445937755599238</v>
       </c>
       <c r="C31">
-        <v>54.93455624306104</v>
+        <v>54.36880010301667</v>
       </c>
       <c r="D31">
-        <v>75.67295624306104</v>
+        <v>75.82480010301667</v>
       </c>
       <c r="E31">
-        <v>18.5504</v>
+        <v>19.268</v>
       </c>
       <c r="F31">
-        <v>20.8104</v>
+        <v>21.528</v>
       </c>
       <c r="G31">
         <v>0.07199999999999999</v>
@@ -3823,28 +3823,28 @@
         <v>5.04</v>
       </c>
       <c r="M31">
-        <v>1.20284112</v>
+        <v>1.2443184</v>
       </c>
       <c r="N31">
-        <v>3.83715888</v>
+        <v>3.7956816</v>
       </c>
       <c r="O31">
-        <v>0.767431776</v>
+        <v>0.7591363200000001</v>
       </c>
       <c r="P31">
-        <v>3.069727104</v>
+        <v>3.03654528</v>
       </c>
       <c r="Q31">
-        <v>5.249727104</v>
+        <v>5.21654528</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1001793671827163</v>
+        <v>0.1008391107942748</v>
       </c>
       <c r="T31">
-        <v>0.9169142532745688</v>
+        <v>0.9280384783673752</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.190079567615712</v>
+        <v>4.050410248695188</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08445937755599238</v>
+        <v>0.08524980441225624</v>
       </c>
       <c r="C32">
-        <v>54.36880010301667</v>
+        <v>52.1319540822774</v>
       </c>
       <c r="D32">
-        <v>75.82480010301667</v>
+        <v>74.3055540822774</v>
       </c>
       <c r="E32">
-        <v>19.268</v>
+        <v>19.98560000000001</v>
       </c>
       <c r="F32">
-        <v>21.528</v>
+        <v>22.2456</v>
       </c>
       <c r="G32">
         <v>0.07199999999999999</v>
@@ -3905,45 +3905,45 @@
         <v>5.04</v>
       </c>
       <c r="M32">
-        <v>1.2443184</v>
+        <v>1.36365528</v>
       </c>
       <c r="N32">
-        <v>3.7956816</v>
+        <v>3.67634472</v>
       </c>
       <c r="O32">
-        <v>0.7591363200000001</v>
+        <v>0.735268944</v>
       </c>
       <c r="P32">
-        <v>3.03654528</v>
+        <v>2.941075776</v>
       </c>
       <c r="Q32">
-        <v>5.21654528</v>
+        <v>5.121075776</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1008391107942748</v>
+        <v>0.101517977409067</v>
       </c>
       <c r="T32">
-        <v>0.9280384783673752</v>
+        <v>0.9394851447672194</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.050410248695188</v>
+        <v>3.69594872979922</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08524980441225624</v>
+        <v>0.08520023126852008</v>
       </c>
       <c r="C33">
-        <v>52.1319540822774</v>
+        <v>51.50784490185688</v>
       </c>
       <c r="D33">
-        <v>74.3055540822774</v>
+        <v>74.39904490185688</v>
       </c>
       <c r="E33">
-        <v>19.98560000000001</v>
+        <v>20.7032</v>
       </c>
       <c r="F33">
-        <v>22.2456</v>
+        <v>22.9632</v>
       </c>
       <c r="G33">
         <v>0.07199999999999999</v>
@@ -3987,28 +3987,28 @@
         <v>5.04</v>
       </c>
       <c r="M33">
-        <v>1.36365528</v>
+        <v>1.40764416</v>
       </c>
       <c r="N33">
-        <v>3.67634472</v>
+        <v>3.63235584</v>
       </c>
       <c r="O33">
-        <v>0.735268944</v>
+        <v>0.726471168</v>
       </c>
       <c r="P33">
-        <v>2.941075776</v>
+        <v>2.905884672</v>
       </c>
       <c r="Q33">
-        <v>5.121075776</v>
+        <v>5.085884672</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.101517977409067</v>
+        <v>0.1022168106890001</v>
       </c>
       <c r="T33">
-        <v>0.9394851447672194</v>
+        <v>0.9512684778258826</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.69594872979922</v>
+        <v>3.580450331992994</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08520023126852008</v>
+        <v>0.08588985812478393</v>
       </c>
       <c r="C34">
-        <v>51.50784490185688</v>
+        <v>49.51043045888728</v>
       </c>
       <c r="D34">
-        <v>74.39904490185688</v>
+        <v>73.11923045888729</v>
       </c>
       <c r="E34">
-        <v>20.7032</v>
+        <v>21.4208</v>
       </c>
       <c r="F34">
-        <v>22.9632</v>
+        <v>23.6808</v>
       </c>
       <c r="G34">
         <v>0.07199999999999999</v>
@@ -4069,45 +4069,45 @@
         <v>5.04</v>
       </c>
       <c r="M34">
-        <v>1.40764416</v>
+        <v>1.51793928</v>
       </c>
       <c r="N34">
-        <v>3.63235584</v>
+        <v>3.52206072</v>
       </c>
       <c r="O34">
-        <v>0.726471168</v>
+        <v>0.704412144</v>
       </c>
       <c r="P34">
-        <v>2.905884672</v>
+        <v>2.817648576</v>
       </c>
       <c r="Q34">
-        <v>5.085884672</v>
+        <v>4.997648576</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1022168106890001</v>
+        <v>0.1029365046638566</v>
       </c>
       <c r="T34">
-        <v>0.9512684778258826</v>
+        <v>0.9634035521698792</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.580450331992994</v>
+        <v>3.320290914403374</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08588985812478393</v>
+        <v>0.08586268498104777</v>
       </c>
       <c r="C35">
-        <v>49.51043045888728</v>
+        <v>48.84242472247889</v>
       </c>
       <c r="D35">
-        <v>73.11923045888729</v>
+        <v>73.16882472247889</v>
       </c>
       <c r="E35">
-        <v>21.4208</v>
+        <v>22.1384</v>
       </c>
       <c r="F35">
-        <v>23.6808</v>
+        <v>24.3984</v>
       </c>
       <c r="G35">
         <v>0.07199999999999999</v>
@@ -4151,28 +4151,28 @@
         <v>5.04</v>
       </c>
       <c r="M35">
-        <v>1.51793928</v>
+        <v>1.56393744</v>
       </c>
       <c r="N35">
-        <v>3.52206072</v>
+        <v>3.47606256</v>
       </c>
       <c r="O35">
-        <v>0.704412144</v>
+        <v>0.695212512</v>
       </c>
       <c r="P35">
-        <v>2.817648576</v>
+        <v>2.780850048</v>
       </c>
       <c r="Q35">
-        <v>4.997648576</v>
+        <v>4.960850047999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1029365046638566</v>
+        <v>0.1036780075470421</v>
       </c>
       <c r="T35">
-        <v>0.9634035521698792</v>
+        <v>0.9759063560394512</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.320290914403374</v>
+        <v>3.222635299273863</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08586268498104777</v>
+        <v>0.08583551183731163</v>
       </c>
       <c r="C36">
-        <v>48.84242472247889</v>
+        <v>48.17448630790504</v>
       </c>
       <c r="D36">
-        <v>73.16882472247889</v>
+        <v>73.21848630790504</v>
       </c>
       <c r="E36">
-        <v>22.1384</v>
+        <v>22.856</v>
       </c>
       <c r="F36">
-        <v>24.3984</v>
+        <v>25.116</v>
       </c>
       <c r="G36">
         <v>0.07199999999999999</v>
@@ -4233,28 +4233,28 @@
         <v>5.04</v>
       </c>
       <c r="M36">
-        <v>1.56393744</v>
+        <v>1.6099356</v>
       </c>
       <c r="N36">
-        <v>3.47606256</v>
+        <v>3.4300644</v>
       </c>
       <c r="O36">
-        <v>0.695212512</v>
+        <v>0.68601288</v>
       </c>
       <c r="P36">
-        <v>2.780850048</v>
+        <v>2.74405152</v>
       </c>
       <c r="Q36">
-        <v>4.960850047999999</v>
+        <v>4.92405152</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1036780075470421</v>
+        <v>0.1044423259035563</v>
       </c>
       <c r="T36">
-        <v>0.9759063560394512</v>
+        <v>0.9887938615665487</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.222635299273863</v>
+        <v>3.130560005008896</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08583551183731163</v>
+        <v>0.08580833869357546</v>
       </c>
       <c r="C37">
-        <v>48.17448630790504</v>
+        <v>47.50661535233819</v>
       </c>
       <c r="D37">
-        <v>73.21848630790504</v>
+        <v>73.26821535233819</v>
       </c>
       <c r="E37">
-        <v>22.856</v>
+        <v>23.57360000000001</v>
       </c>
       <c r="F37">
-        <v>25.116</v>
+        <v>25.8336</v>
       </c>
       <c r="G37">
         <v>0.07199999999999999</v>
@@ -4315,28 +4315,28 @@
         <v>5.04</v>
       </c>
       <c r="M37">
-        <v>1.6099356</v>
+        <v>1.65593376</v>
       </c>
       <c r="N37">
-        <v>3.4300644</v>
+        <v>3.38406624</v>
       </c>
       <c r="O37">
-        <v>0.68601288</v>
+        <v>0.676813248</v>
       </c>
       <c r="P37">
-        <v>2.74405152</v>
+        <v>2.707252992</v>
       </c>
       <c r="Q37">
-        <v>4.92405152</v>
+        <v>4.887252992</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1044423259035563</v>
+        <v>0.1052305292087117</v>
       </c>
       <c r="T37">
-        <v>0.9887938615665487</v>
+        <v>1.002084101641368</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.130560005008896</v>
+        <v>3.043600004869759</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08580833869357547</v>
+        <v>0.08808996554983933</v>
       </c>
       <c r="C38">
-        <v>47.50661535233816</v>
+        <v>42.83605096267922</v>
       </c>
       <c r="D38">
-        <v>73.26821535233816</v>
+        <v>69.31525096267922</v>
       </c>
       <c r="E38">
-        <v>23.5736</v>
+        <v>24.2912</v>
       </c>
       <c r="F38">
-        <v>25.8336</v>
+        <v>26.5512</v>
       </c>
       <c r="G38">
         <v>0.07199999999999999</v>
@@ -4397,45 +4397,45 @@
         <v>5.04</v>
       </c>
       <c r="M38">
-        <v>1.65593376</v>
+        <v>1.90903128</v>
       </c>
       <c r="N38">
-        <v>3.38406624</v>
+        <v>3.13096872</v>
       </c>
       <c r="O38">
-        <v>0.6768132480000001</v>
+        <v>0.6261937440000001</v>
       </c>
       <c r="P38">
-        <v>2.707252992</v>
+        <v>2.504774976</v>
       </c>
       <c r="Q38">
-        <v>4.887252992</v>
+        <v>4.684774976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1052305292087117</v>
+        <v>0.1060437548410148</v>
       </c>
       <c r="T38">
-        <v>1.002084101641368</v>
+        <v>1.015796254099515</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.04360000486976</v>
+        <v>2.640082461089899</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08808996554983933</v>
+        <v>0.08812519240610317</v>
       </c>
       <c r="C39">
-        <v>42.83605096267922</v>
+        <v>42.06076053662926</v>
       </c>
       <c r="D39">
-        <v>69.31525096267922</v>
+        <v>69.25756053662926</v>
       </c>
       <c r="E39">
-        <v>24.2912</v>
+        <v>25.0088</v>
       </c>
       <c r="F39">
-        <v>26.5512</v>
+        <v>27.2688</v>
       </c>
       <c r="G39">
         <v>0.07199999999999999</v>
@@ -4479,28 +4479,28 @@
         <v>5.04</v>
       </c>
       <c r="M39">
-        <v>1.90903128</v>
+        <v>1.96062672</v>
       </c>
       <c r="N39">
-        <v>3.13096872</v>
+        <v>3.07937328</v>
       </c>
       <c r="O39">
-        <v>0.6261937440000001</v>
+        <v>0.6158746559999999</v>
       </c>
       <c r="P39">
-        <v>2.504774976</v>
+        <v>2.463498624</v>
       </c>
       <c r="Q39">
-        <v>4.684774976</v>
+        <v>4.643498623999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1060437548410148</v>
+        <v>0.1068832135582309</v>
       </c>
       <c r="T39">
-        <v>1.015796254099515</v>
+        <v>1.029950734056311</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.640082461089899</v>
+        <v>2.57060660685069</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08812519240610317</v>
+        <v>0.08816041926236701</v>
       </c>
       <c r="C40">
-        <v>42.06076053662926</v>
+        <v>41.28556606110962</v>
       </c>
       <c r="D40">
-        <v>69.25756053662926</v>
+        <v>69.19996606110962</v>
       </c>
       <c r="E40">
-        <v>25.0088</v>
+        <v>25.72640000000001</v>
       </c>
       <c r="F40">
-        <v>27.2688</v>
+        <v>27.9864</v>
       </c>
       <c r="G40">
         <v>0.07199999999999999</v>
@@ -4561,28 +4561,28 @@
         <v>5.04</v>
       </c>
       <c r="M40">
-        <v>1.96062672</v>
+        <v>2.01222216</v>
       </c>
       <c r="N40">
-        <v>3.07937328</v>
+        <v>3.02777784</v>
       </c>
       <c r="O40">
-        <v>0.6158746559999999</v>
+        <v>0.605555568</v>
       </c>
       <c r="P40">
-        <v>2.463498624</v>
+        <v>2.422222272</v>
       </c>
       <c r="Q40">
-        <v>4.643498623999999</v>
+        <v>4.602222272</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1068832135582309</v>
+        <v>0.1077501955120771</v>
       </c>
       <c r="T40">
-        <v>1.029950734056311</v>
+        <v>1.044569295323167</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.57060660685069</v>
+        <v>2.504693616931442</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08816041926236701</v>
+        <v>0.08944364611863086</v>
       </c>
       <c r="C41">
-        <v>41.28556606110962</v>
+        <v>38.53332269834402</v>
       </c>
       <c r="D41">
-        <v>69.19996606110962</v>
+        <v>67.16532269834403</v>
       </c>
       <c r="E41">
-        <v>25.72640000000001</v>
+        <v>26.444</v>
       </c>
       <c r="F41">
-        <v>27.9864</v>
+        <v>28.704</v>
       </c>
       <c r="G41">
         <v>0.07199999999999999</v>
@@ -4643,45 +4643,45 @@
         <v>5.04</v>
       </c>
       <c r="M41">
-        <v>2.01222216</v>
+        <v>2.1757632</v>
       </c>
       <c r="N41">
-        <v>3.02777784</v>
+        <v>2.8642368</v>
       </c>
       <c r="O41">
-        <v>0.605555568</v>
+        <v>0.5728473599999999</v>
       </c>
       <c r="P41">
-        <v>2.422222272</v>
+        <v>2.29138944</v>
       </c>
       <c r="Q41">
-        <v>4.602222272</v>
+        <v>4.471389439999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1077501955120771</v>
+        <v>0.1086460768643848</v>
       </c>
       <c r="T41">
-        <v>1.044569295323167</v>
+        <v>1.059675141965585</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.504693616931442</v>
+        <v>2.31642855251895</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08944364611863086</v>
+        <v>0.0895100729748947</v>
       </c>
       <c r="C42">
-        <v>38.53332269834402</v>
+        <v>37.71365054579099</v>
       </c>
       <c r="D42">
-        <v>67.16532269834403</v>
+        <v>67.06325054579099</v>
       </c>
       <c r="E42">
-        <v>26.444</v>
+        <v>27.16160000000001</v>
       </c>
       <c r="F42">
-        <v>28.704</v>
+        <v>29.42160000000001</v>
       </c>
       <c r="G42">
         <v>0.07199999999999999</v>
@@ -4725,28 +4725,28 @@
         <v>5.04</v>
       </c>
       <c r="M42">
-        <v>2.1757632</v>
+        <v>2.230157280000001</v>
       </c>
       <c r="N42">
-        <v>2.8642368</v>
+        <v>2.809842719999999</v>
       </c>
       <c r="O42">
-        <v>0.5728473599999999</v>
+        <v>0.5619685439999998</v>
       </c>
       <c r="P42">
-        <v>2.29138944</v>
+        <v>2.247874175999999</v>
       </c>
       <c r="Q42">
-        <v>4.471389439999999</v>
+        <v>4.427874176</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1086460768643848</v>
+        <v>0.1095723270760927</v>
       </c>
       <c r="T42">
-        <v>1.059675141965585</v>
+        <v>1.07529305120605</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.31642855251895</v>
+        <v>2.259930295140439</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0895100729748947</v>
+        <v>0.08957649983115853</v>
       </c>
       <c r="C43">
-        <v>37.71365054579099</v>
+        <v>36.89428816365053</v>
       </c>
       <c r="D43">
-        <v>67.06325054579099</v>
+        <v>66.96148816365053</v>
       </c>
       <c r="E43">
-        <v>27.16160000000001</v>
+        <v>27.8792</v>
       </c>
       <c r="F43">
-        <v>29.42160000000001</v>
+        <v>30.13920000000001</v>
       </c>
       <c r="G43">
         <v>0.07199999999999999</v>
@@ -4807,28 +4807,28 @@
         <v>5.04</v>
       </c>
       <c r="M43">
-        <v>2.230157280000001</v>
+        <v>2.28455136</v>
       </c>
       <c r="N43">
-        <v>2.809842719999999</v>
+        <v>2.75544864</v>
       </c>
       <c r="O43">
-        <v>0.5619685439999998</v>
+        <v>0.5510897279999999</v>
       </c>
       <c r="P43">
-        <v>2.247874175999999</v>
+        <v>2.204358912</v>
       </c>
       <c r="Q43">
-        <v>4.427874176</v>
+        <v>4.384358912</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1095723270760927</v>
+        <v>0.1105305169502734</v>
       </c>
       <c r="T43">
-        <v>1.07529305120605</v>
+        <v>1.091449509041014</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.259930295140439</v>
+        <v>2.206122430970429</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08957649983115855</v>
+        <v>0.08964292668742241</v>
       </c>
       <c r="C44">
-        <v>36.8942881636505</v>
+        <v>36.07523414391379</v>
       </c>
       <c r="D44">
-        <v>66.9614881636505</v>
+        <v>66.86003414391379</v>
       </c>
       <c r="E44">
-        <v>27.8792</v>
+        <v>28.5968</v>
       </c>
       <c r="F44">
-        <v>30.1392</v>
+        <v>30.8568</v>
       </c>
       <c r="G44">
         <v>0.07199999999999999</v>
@@ -4889,28 +4889,28 @@
         <v>5.04</v>
       </c>
       <c r="M44">
-        <v>2.28455136</v>
+        <v>2.33894544</v>
       </c>
       <c r="N44">
-        <v>2.75544864</v>
+        <v>2.70105456</v>
       </c>
       <c r="O44">
-        <v>0.5510897279999999</v>
+        <v>0.5402109119999999</v>
       </c>
       <c r="P44">
-        <v>2.204358912</v>
+        <v>2.160843648</v>
       </c>
       <c r="Q44">
-        <v>4.384358912</v>
+        <v>4.340843648</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1105305169502734</v>
+        <v>0.1115223275217937</v>
       </c>
       <c r="T44">
-        <v>1.091449509041014</v>
+        <v>1.108172860133346</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.206122430970429</v>
+        <v>2.154817258157163</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08964292668742241</v>
+        <v>0.08970935354368624</v>
       </c>
       <c r="C45">
-        <v>36.07523414391379</v>
+        <v>35.25648708709244</v>
       </c>
       <c r="D45">
-        <v>66.86003414391379</v>
+        <v>66.75888708709243</v>
       </c>
       <c r="E45">
-        <v>28.5968</v>
+        <v>29.3144</v>
       </c>
       <c r="F45">
-        <v>30.8568</v>
+        <v>31.5744</v>
       </c>
       <c r="G45">
         <v>0.07199999999999999</v>
@@ -4971,28 +4971,28 @@
         <v>5.04</v>
       </c>
       <c r="M45">
-        <v>2.33894544</v>
+        <v>2.39333952</v>
       </c>
       <c r="N45">
-        <v>2.70105456</v>
+        <v>2.64666048</v>
       </c>
       <c r="O45">
-        <v>0.5402109119999999</v>
+        <v>0.529332096</v>
       </c>
       <c r="P45">
-        <v>2.160843648</v>
+        <v>2.117328384</v>
       </c>
       <c r="Q45">
-        <v>4.340843648</v>
+        <v>4.297328384</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1115223275217937</v>
+        <v>0.1125495598994397</v>
       </c>
       <c r="T45">
-        <v>1.108172860133346</v>
+        <v>1.125493473764689</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.154817258157163</v>
+        <v>2.105844138653591</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08970935354368624</v>
+        <v>0.08977578039995009</v>
       </c>
       <c r="C46">
-        <v>35.25648708709244</v>
+        <v>34.43804560215374</v>
       </c>
       <c r="D46">
-        <v>66.75888708709243</v>
+        <v>66.65804560215373</v>
       </c>
       <c r="E46">
-        <v>29.3144</v>
+        <v>30.032</v>
       </c>
       <c r="F46">
-        <v>31.5744</v>
+        <v>32.292</v>
       </c>
       <c r="G46">
         <v>0.07199999999999999</v>
@@ -5053,28 +5053,28 @@
         <v>5.04</v>
       </c>
       <c r="M46">
-        <v>2.39333952</v>
+        <v>2.4477336</v>
       </c>
       <c r="N46">
-        <v>2.64666048</v>
+        <v>2.5922664</v>
       </c>
       <c r="O46">
-        <v>0.529332096</v>
+        <v>0.51845328</v>
       </c>
       <c r="P46">
-        <v>2.117328384</v>
+        <v>2.07381312</v>
       </c>
       <c r="Q46">
-        <v>4.297328384</v>
+        <v>4.253813119999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1125495598994397</v>
+        <v>0.1136141461817274</v>
       </c>
       <c r="T46">
-        <v>1.125493473764689</v>
+        <v>1.143443927891717</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.105844138653591</v>
+        <v>2.059047602239067</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08977578039995009</v>
+        <v>0.08984220725621393</v>
       </c>
       <c r="C47">
-        <v>34.43804560215374</v>
+        <v>33.61990830645726</v>
       </c>
       <c r="D47">
-        <v>66.65804560215373</v>
+        <v>66.55750830645727</v>
       </c>
       <c r="E47">
-        <v>30.032</v>
+        <v>30.74960000000001</v>
       </c>
       <c r="F47">
-        <v>32.292</v>
+        <v>33.00960000000001</v>
       </c>
       <c r="G47">
         <v>0.07199999999999999</v>
@@ -5135,28 +5135,28 @@
         <v>5.04</v>
       </c>
       <c r="M47">
-        <v>2.4477336</v>
+        <v>2.502127680000001</v>
       </c>
       <c r="N47">
-        <v>2.5922664</v>
+        <v>2.53787232</v>
       </c>
       <c r="O47">
-        <v>0.51845328</v>
+        <v>0.5075744639999999</v>
       </c>
       <c r="P47">
-        <v>2.07381312</v>
+        <v>2.030297856</v>
       </c>
       <c r="Q47">
-        <v>4.253813119999999</v>
+        <v>4.210297856</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1136141461817274</v>
+        <v>0.1147181615855813</v>
       </c>
       <c r="T47">
-        <v>1.143443927891717</v>
+        <v>1.162059213653081</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.059047602239067</v>
+        <v>2.014285697842565</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08984220725621393</v>
+        <v>0.09524783411247778</v>
       </c>
       <c r="C48">
-        <v>33.61990830645726</v>
+        <v>25.62625545510294</v>
       </c>
       <c r="D48">
-        <v>66.55750830645727</v>
+        <v>59.28145545510294</v>
       </c>
       <c r="E48">
-        <v>30.74960000000001</v>
+        <v>31.46720000000001</v>
       </c>
       <c r="F48">
-        <v>33.00960000000001</v>
+        <v>33.7272</v>
       </c>
       <c r="G48">
         <v>0.07199999999999999</v>
@@ -5217,45 +5217,45 @@
         <v>5.04</v>
       </c>
       <c r="M48">
-        <v>2.502127680000001</v>
+        <v>3.035448</v>
       </c>
       <c r="N48">
-        <v>2.53787232</v>
+        <v>2.004552</v>
       </c>
       <c r="O48">
-        <v>0.5075744639999999</v>
+        <v>0.4009104</v>
       </c>
       <c r="P48">
-        <v>2.030297856</v>
+        <v>1.6036416</v>
       </c>
       <c r="Q48">
-        <v>4.210297856</v>
+        <v>3.7836416</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1147181615855813</v>
+        <v>0.1158638379480713</v>
       </c>
       <c r="T48">
-        <v>1.162059213653081</v>
+        <v>1.18137696302808</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.014285697842565</v>
+        <v>1.660380938826822</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09524783411247778</v>
+        <v>0.09542786096874162</v>
       </c>
       <c r="C49">
-        <v>25.62625545510294</v>
+        <v>24.69360983653298</v>
       </c>
       <c r="D49">
-        <v>59.28145545510294</v>
+        <v>59.06640983653298</v>
       </c>
       <c r="E49">
-        <v>31.46720000000001</v>
+        <v>32.18480000000001</v>
       </c>
       <c r="F49">
-        <v>33.7272</v>
+        <v>34.44480000000001</v>
       </c>
       <c r="G49">
         <v>0.07199999999999999</v>
@@ -5299,28 +5299,28 @@
         <v>5.04</v>
       </c>
       <c r="M49">
-        <v>3.035448</v>
+        <v>3.100032000000001</v>
       </c>
       <c r="N49">
-        <v>2.004552</v>
+        <v>1.939967999999999</v>
       </c>
       <c r="O49">
-        <v>0.4009104</v>
+        <v>0.3879935999999999</v>
       </c>
       <c r="P49">
-        <v>1.6036416</v>
+        <v>1.5519744</v>
       </c>
       <c r="Q49">
-        <v>3.7836416</v>
+        <v>3.731974399999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1158638379480713</v>
+        <v>0.1170535787860416</v>
       </c>
       <c r="T49">
-        <v>1.18137696302808</v>
+        <v>1.201437702763656</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.660380938826822</v>
+        <v>1.62578966926793</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09542786096874162</v>
+        <v>0.09560788782500547</v>
       </c>
       <c r="C50">
-        <v>24.69360983653299</v>
+        <v>23.76251875032143</v>
       </c>
       <c r="D50">
-        <v>59.06640983653298</v>
+        <v>58.85291875032144</v>
       </c>
       <c r="E50">
-        <v>32.1848</v>
+        <v>32.90240000000001</v>
       </c>
       <c r="F50">
-        <v>34.4448</v>
+        <v>35.16240000000001</v>
       </c>
       <c r="G50">
         <v>0.07199999999999999</v>
@@ -5381,28 +5381,28 @@
         <v>5.04</v>
       </c>
       <c r="M50">
-        <v>3.100032</v>
+        <v>3.164616000000001</v>
       </c>
       <c r="N50">
-        <v>1.939968</v>
+        <v>1.875383999999999</v>
       </c>
       <c r="O50">
-        <v>0.3879936</v>
+        <v>0.3750767999999999</v>
       </c>
       <c r="P50">
-        <v>1.5519744</v>
+        <v>1.5003072</v>
       </c>
       <c r="Q50">
-        <v>3.731974399999999</v>
+        <v>3.680307199999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1170535787860416</v>
+        <v>0.1182899761274617</v>
       </c>
       <c r="T50">
-        <v>1.201437702763656</v>
+        <v>1.222285138175137</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.62578966926793</v>
+        <v>1.592610288262462</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09560788782500547</v>
+        <v>0.09578791468126932</v>
       </c>
       <c r="C51">
-        <v>23.76251875032143</v>
+        <v>22.83296540095433</v>
       </c>
       <c r="D51">
-        <v>58.85291875032144</v>
+        <v>58.64096540095433</v>
       </c>
       <c r="E51">
-        <v>32.90240000000001</v>
+        <v>33.62</v>
       </c>
       <c r="F51">
-        <v>35.16240000000001</v>
+        <v>35.88</v>
       </c>
       <c r="G51">
         <v>0.07199999999999999</v>
@@ -5463,28 +5463,28 @@
         <v>5.04</v>
       </c>
       <c r="M51">
-        <v>3.164616000000001</v>
+        <v>3.2292</v>
       </c>
       <c r="N51">
-        <v>1.875383999999999</v>
+        <v>1.8108</v>
       </c>
       <c r="O51">
-        <v>0.3750767999999999</v>
+        <v>0.36216</v>
       </c>
       <c r="P51">
-        <v>1.5003072</v>
+        <v>1.44864</v>
       </c>
       <c r="Q51">
-        <v>3.680307199999999</v>
+        <v>3.62864</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1182899761274617</v>
+        <v>0.1195758293625386</v>
       </c>
       <c r="T51">
-        <v>1.222285138175137</v>
+        <v>1.243966471003077</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.592610288262462</v>
+        <v>1.560758082497213</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09578791468126932</v>
+        <v>0.09596794153753316</v>
       </c>
       <c r="C52">
-        <v>22.83296540095433</v>
+        <v>21.90493323399943</v>
       </c>
       <c r="D52">
-        <v>58.64096540095433</v>
+        <v>58.43053323399943</v>
       </c>
       <c r="E52">
-        <v>33.62</v>
+        <v>34.3376</v>
       </c>
       <c r="F52">
-        <v>35.88</v>
+        <v>36.5976</v>
       </c>
       <c r="G52">
         <v>0.07199999999999999</v>
@@ -5545,28 +5545,28 @@
         <v>5.04</v>
       </c>
       <c r="M52">
-        <v>3.2292</v>
+        <v>3.293784</v>
       </c>
       <c r="N52">
-        <v>1.8108</v>
+        <v>1.746216</v>
       </c>
       <c r="O52">
-        <v>0.36216</v>
+        <v>0.3492432</v>
       </c>
       <c r="P52">
-        <v>1.44864</v>
+        <v>1.3969728</v>
       </c>
       <c r="Q52">
-        <v>3.62864</v>
+        <v>3.5769728</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1195758293625386</v>
+        <v>0.1209141664031289</v>
       </c>
       <c r="T52">
-        <v>1.243966471003077</v>
+        <v>1.266532756191342</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.560758082497213</v>
+        <v>1.530154982840405</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09596794153753316</v>
+        <v>0.09614796839379701</v>
       </c>
       <c r="C53">
-        <v>21.90493323399943</v>
+        <v>20.97840593179603</v>
       </c>
       <c r="D53">
-        <v>58.43053323399943</v>
+        <v>58.22160593179603</v>
       </c>
       <c r="E53">
-        <v>34.3376</v>
+        <v>35.05520000000001</v>
       </c>
       <c r="F53">
-        <v>36.5976</v>
+        <v>37.3152</v>
       </c>
       <c r="G53">
         <v>0.07199999999999999</v>
@@ -5627,28 +5627,28 @@
         <v>5.04</v>
       </c>
       <c r="M53">
-        <v>3.293784</v>
+        <v>3.358368</v>
       </c>
       <c r="N53">
-        <v>1.746216</v>
+        <v>1.681632</v>
       </c>
       <c r="O53">
-        <v>0.3492432</v>
+        <v>0.3363263999999999</v>
       </c>
       <c r="P53">
-        <v>1.3969728</v>
+        <v>1.3453056</v>
       </c>
       <c r="Q53">
-        <v>3.5769728</v>
+        <v>3.525305599999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1209141664031289</v>
+        <v>0.1223082674870771</v>
       </c>
       <c r="T53">
-        <v>1.266532756191342</v>
+        <v>1.290039303262451</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.530154982840405</v>
+        <v>1.500728925478089</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09614796839379701</v>
+        <v>0.1223478750802848</v>
       </c>
       <c r="C54">
-        <v>20.97840593179603</v>
+        <v>0.3333991820900266</v>
       </c>
       <c r="D54">
-        <v>58.22160593179603</v>
+        <v>38.29419918209003</v>
       </c>
       <c r="E54">
-        <v>35.05520000000001</v>
+        <v>35.7728</v>
       </c>
       <c r="F54">
-        <v>37.3152</v>
+        <v>38.0328</v>
       </c>
       <c r="G54">
         <v>0.07199999999999999</v>
@@ -5709,45 +5709,45 @@
         <v>5.04</v>
       </c>
       <c r="M54">
-        <v>3.358368</v>
+        <v>5.583215040000001</v>
       </c>
       <c r="N54">
-        <v>1.681632</v>
+        <v>-0.5432150400000006</v>
       </c>
       <c r="O54">
-        <v>0.3363263999999999</v>
+        <v>-0.1086430080000001</v>
       </c>
       <c r="P54">
-        <v>1.3453056</v>
+        <v>-0.4345720320000005</v>
       </c>
       <c r="Q54">
-        <v>3.525305599999999</v>
+        <v>1.745427967999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1223082674870771</v>
+        <v>0.124661059197361</v>
       </c>
       <c r="T54">
-        <v>1.290039303262451</v>
+        <v>1.329710751569249</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2</v>
+        <v>0.1805411385336861</v>
       </c>
       <c r="W54">
-        <v>0.07199999999999999</v>
+        <v>0.1202965608632549</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.500728925478089</v>
+        <v>0.9027056926684306</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1223478750802848</v>
+        <v>0.1233578750802848</v>
       </c>
       <c r="C55">
-        <v>0.3333991820900266</v>
+        <v>-0.8828882965686233</v>
       </c>
       <c r="D55">
-        <v>38.29419918209003</v>
+        <v>37.79551170343138</v>
       </c>
       <c r="E55">
-        <v>35.7728</v>
+        <v>36.49040000000001</v>
       </c>
       <c r="F55">
-        <v>38.0328</v>
+        <v>38.75040000000001</v>
       </c>
       <c r="G55">
         <v>0.07199999999999999</v>
@@ -5791,37 +5791,37 @@
         <v>5.04</v>
       </c>
       <c r="M55">
-        <v>5.583215040000001</v>
+        <v>5.688558720000001</v>
       </c>
       <c r="N55">
-        <v>-0.5432150400000006</v>
+        <v>-0.6485587200000014</v>
       </c>
       <c r="O55">
-        <v>-0.1086430080000001</v>
+        <v>-0.1297117440000003</v>
       </c>
       <c r="P55">
-        <v>-0.4345720320000005</v>
+        <v>-0.5188469760000011</v>
       </c>
       <c r="Q55">
-        <v>1.745427967999999</v>
+        <v>1.661153023999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.124661059197361</v>
+        <v>0.1263754300494775</v>
       </c>
       <c r="T55">
-        <v>1.329710751569249</v>
+        <v>1.358617507038146</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1805411385336861</v>
+        <v>0.1771977841163956</v>
       </c>
       <c r="W55">
-        <v>0.1202965608632549</v>
+        <v>0.1207873652917131</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9027056926684306</v>
+        <v>0.8859889205819781</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1233578750802848</v>
+        <v>0.1243678750802848</v>
       </c>
       <c r="C56">
-        <v>-0.8828882965686233</v>
+        <v>-2.086354393640214</v>
       </c>
       <c r="D56">
-        <v>37.79551170343138</v>
+        <v>37.30964560635979</v>
       </c>
       <c r="E56">
-        <v>36.49040000000001</v>
+        <v>37.20800000000001</v>
       </c>
       <c r="F56">
-        <v>38.75040000000001</v>
+        <v>39.468</v>
       </c>
       <c r="G56">
         <v>0.07199999999999999</v>
@@ -5873,37 +5873,37 @@
         <v>5.04</v>
       </c>
       <c r="M56">
-        <v>5.688558720000001</v>
+        <v>5.793902400000001</v>
       </c>
       <c r="N56">
-        <v>-0.6485587200000014</v>
+        <v>-0.7539024000000012</v>
       </c>
       <c r="O56">
-        <v>-0.1297117440000003</v>
+        <v>-0.1507804800000002</v>
       </c>
       <c r="P56">
-        <v>-0.5188469760000011</v>
+        <v>-0.603121920000001</v>
       </c>
       <c r="Q56">
-        <v>1.661153023999999</v>
+        <v>1.576878079999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1263754300494775</v>
+        <v>0.1281659951616882</v>
       </c>
       <c r="T56">
-        <v>1.358617507038146</v>
+        <v>1.388809007194549</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1771977841163956</v>
+        <v>0.1739760062233703</v>
       </c>
       <c r="W56">
-        <v>0.1207873652917131</v>
+        <v>0.1212603222864092</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8859889205819781</v>
+        <v>0.8698800311168512</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1243678750802848</v>
+        <v>0.1253778750802848</v>
       </c>
       <c r="C57">
-        <v>-2.086354393640214</v>
+        <v>-3.277487294894556</v>
       </c>
       <c r="D57">
-        <v>37.30964560635979</v>
+        <v>36.83611270510545</v>
       </c>
       <c r="E57">
-        <v>37.20800000000001</v>
+        <v>37.92560000000001</v>
       </c>
       <c r="F57">
-        <v>39.468</v>
+        <v>40.18560000000001</v>
       </c>
       <c r="G57">
         <v>0.07199999999999999</v>
@@ -5955,37 +5955,37 @@
         <v>5.04</v>
       </c>
       <c r="M57">
-        <v>5.793902400000001</v>
+        <v>5.899246080000002</v>
       </c>
       <c r="N57">
-        <v>-0.7539024000000012</v>
+        <v>-0.8592460800000019</v>
       </c>
       <c r="O57">
-        <v>-0.1507804800000002</v>
+        <v>-0.1718492160000004</v>
       </c>
       <c r="P57">
-        <v>-0.603121920000001</v>
+        <v>-0.6873968640000016</v>
       </c>
       <c r="Q57">
-        <v>1.576878079999999</v>
+        <v>1.492603135999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1281659951616882</v>
+        <v>0.1300379495971811</v>
       </c>
       <c r="T57">
-        <v>1.388809007194549</v>
+        <v>1.420372848267153</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1739760062233703</v>
+        <v>0.1708692918265243</v>
       </c>
       <c r="W57">
-        <v>0.1212603222864092</v>
+        <v>0.1217163879598662</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8698800311168512</v>
+        <v>0.8543464591326216</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1253778750802848</v>
+        <v>0.1263878750802848</v>
       </c>
       <c r="C58">
-        <v>-3.277487294894556</v>
+        <v>-4.45675071256246</v>
       </c>
       <c r="D58">
-        <v>36.83611270510545</v>
+        <v>36.37444928743754</v>
       </c>
       <c r="E58">
-        <v>37.92560000000001</v>
+        <v>38.64320000000001</v>
       </c>
       <c r="F58">
-        <v>40.18560000000001</v>
+        <v>40.90320000000001</v>
       </c>
       <c r="G58">
         <v>0.07199999999999999</v>
@@ -6037,37 +6037,37 @@
         <v>5.04</v>
       </c>
       <c r="M58">
-        <v>5.899246080000002</v>
+        <v>6.004589760000002</v>
       </c>
       <c r="N58">
-        <v>-0.8592460800000019</v>
+        <v>-0.9645897600000017</v>
       </c>
       <c r="O58">
-        <v>-0.1718492160000004</v>
+        <v>-0.1929179520000004</v>
       </c>
       <c r="P58">
-        <v>-0.6873968640000016</v>
+        <v>-0.7716718080000013</v>
       </c>
       <c r="Q58">
-        <v>1.492603135999998</v>
+        <v>1.408328191999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1300379495971811</v>
+        <v>0.1319969716808365</v>
       </c>
       <c r="T58">
-        <v>1.420372848267153</v>
+        <v>1.45340477497104</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1708692918265243</v>
+        <v>0.1678715849523748</v>
       </c>
       <c r="W58">
-        <v>0.1217163879598662</v>
+        <v>0.1221564513289914</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8543464591326216</v>
+        <v>0.8393579247618739</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1263878750802848</v>
+        <v>0.1273978750802848</v>
       </c>
       <c r="C59">
-        <v>-4.45675071256246</v>
+        <v>-5.624585399975146</v>
       </c>
       <c r="D59">
-        <v>36.37444928743754</v>
+        <v>35.92421460002486</v>
       </c>
       <c r="E59">
-        <v>38.64320000000001</v>
+        <v>39.36080000000001</v>
       </c>
       <c r="F59">
-        <v>40.90320000000001</v>
+        <v>41.62080000000001</v>
       </c>
       <c r="G59">
         <v>0.07199999999999999</v>
@@ -6119,37 +6119,37 @@
         <v>5.04</v>
       </c>
       <c r="M59">
-        <v>6.004589760000002</v>
+        <v>6.109933440000002</v>
       </c>
       <c r="N59">
-        <v>-0.9645897600000017</v>
+        <v>-1.069933440000002</v>
       </c>
       <c r="O59">
-        <v>-0.1929179520000004</v>
+        <v>-0.2139866880000003</v>
       </c>
       <c r="P59">
-        <v>-0.7716718080000013</v>
+        <v>-0.8559467520000013</v>
       </c>
       <c r="Q59">
-        <v>1.408328191999998</v>
+        <v>1.324053247999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1319969716808365</v>
+        <v>0.1340492805303802</v>
       </c>
       <c r="T59">
-        <v>1.45340477497104</v>
+        <v>1.488009650565589</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1678715849523748</v>
+        <v>0.1649772472807821</v>
       </c>
       <c r="W59">
-        <v>0.1221564513289914</v>
+        <v>0.1225813400991812</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8393579247618739</v>
+        <v>0.8248862364039106</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1273978750802848</v>
+        <v>0.1284078750802848</v>
       </c>
       <c r="C60">
-        <v>-5.624585399975139</v>
+        <v>-6.781410555092144</v>
       </c>
       <c r="D60">
-        <v>35.92421460002486</v>
+        <v>35.48498944490785</v>
       </c>
       <c r="E60">
-        <v>39.3608</v>
+        <v>40.0784</v>
       </c>
       <c r="F60">
-        <v>41.6208</v>
+        <v>42.3384</v>
       </c>
       <c r="G60">
         <v>0.07199999999999999</v>
@@ -6201,37 +6201,37 @@
         <v>5.04</v>
       </c>
       <c r="M60">
-        <v>6.109933440000001</v>
+        <v>6.215277120000001</v>
       </c>
       <c r="N60">
-        <v>-1.069933440000001</v>
+        <v>-1.175277120000001</v>
       </c>
       <c r="O60">
-        <v>-0.2139866880000001</v>
+        <v>-0.2350554240000001</v>
       </c>
       <c r="P60">
-        <v>-0.8559467520000006</v>
+        <v>-0.9402216960000004</v>
       </c>
       <c r="Q60">
-        <v>1.324053247999999</v>
+        <v>1.239778303999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1340492805303801</v>
+        <v>0.1362017020067309</v>
       </c>
       <c r="T60">
-        <v>1.488009650565588</v>
+        <v>1.524302568872066</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1649772472807821</v>
+        <v>0.1621810227505994</v>
       </c>
       <c r="W60">
-        <v>0.1225813400991812</v>
+        <v>0.122991825860212</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8248862364039107</v>
+        <v>0.810905113752997</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1284078750802848</v>
+        <v>0.1628725623235474</v>
       </c>
       <c r="C61">
-        <v>-6.781410555092144</v>
+        <v>-17.94534433968414</v>
       </c>
       <c r="D61">
-        <v>35.48498944490785</v>
+        <v>25.03865566031586</v>
       </c>
       <c r="E61">
-        <v>40.0784</v>
+        <v>40.79600000000001</v>
       </c>
       <c r="F61">
-        <v>42.3384</v>
+        <v>43.056</v>
       </c>
       <c r="G61">
         <v>0.07199999999999999</v>
@@ -6283,45 +6283,45 @@
         <v>5.04</v>
       </c>
       <c r="M61">
-        <v>6.215277120000001</v>
+        <v>8.645644800000001</v>
       </c>
       <c r="N61">
-        <v>-1.175277120000001</v>
+        <v>-3.605644800000001</v>
       </c>
       <c r="O61">
-        <v>-0.2350554240000001</v>
+        <v>-0.7211289600000003</v>
       </c>
       <c r="P61">
-        <v>-0.9402216960000004</v>
+        <v>-2.884515840000001</v>
       </c>
       <c r="Q61">
-        <v>1.239778303999999</v>
+        <v>-0.7045158400000013</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1362017020067309</v>
+        <v>0.1410984626650557</v>
       </c>
       <c r="T61">
-        <v>1.524302568872066</v>
+        <v>1.606868988363598</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1621810227505994</v>
+        <v>0.1165904942104492</v>
       </c>
       <c r="W61">
-        <v>0.122991825860212</v>
+        <v>0.1773886287625418</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.810905113752997</v>
+        <v>0.5829524710522458</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1628725623235474</v>
+        <v>0.1644225623235474</v>
       </c>
       <c r="C62">
-        <v>-17.94534433968414</v>
+        <v>-18.99011579436605</v>
       </c>
       <c r="D62">
-        <v>25.03865566031586</v>
+        <v>24.71148420563395</v>
       </c>
       <c r="E62">
-        <v>40.79600000000001</v>
+        <v>41.5136</v>
       </c>
       <c r="F62">
-        <v>43.056</v>
+        <v>43.7736</v>
       </c>
       <c r="G62">
         <v>0.07199999999999999</v>
@@ -6365,37 +6365,37 @@
         <v>5.04</v>
       </c>
       <c r="M62">
-        <v>8.645644800000001</v>
+        <v>8.78973888</v>
       </c>
       <c r="N62">
-        <v>-3.605644800000001</v>
+        <v>-3.74973888</v>
       </c>
       <c r="O62">
-        <v>-0.7211289600000003</v>
+        <v>-0.749947776</v>
       </c>
       <c r="P62">
-        <v>-2.884515840000001</v>
+        <v>-2.999791104</v>
       </c>
       <c r="Q62">
-        <v>-0.7045158400000013</v>
+        <v>-0.8197911040000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1410984626650557</v>
+        <v>0.1435420129898008</v>
       </c>
       <c r="T62">
-        <v>1.606868988363598</v>
+        <v>1.648070757295999</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1165904942104492</v>
+        <v>0.1146791746332287</v>
       </c>
       <c r="W62">
-        <v>0.1773886287625418</v>
+        <v>0.1777724217336477</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5829524710522458</v>
+        <v>0.5733958731661435</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1644225623235474</v>
+        <v>0.1659725623235474</v>
       </c>
       <c r="C63">
-        <v>-18.99011579436605</v>
+        <v>-20.02644745638727</v>
       </c>
       <c r="D63">
-        <v>24.71148420563395</v>
+        <v>24.39275254361273</v>
       </c>
       <c r="E63">
-        <v>41.5136</v>
+        <v>42.23120000000001</v>
       </c>
       <c r="F63">
-        <v>43.7736</v>
+        <v>44.49120000000001</v>
       </c>
       <c r="G63">
         <v>0.07199999999999999</v>
@@ -6447,37 +6447,37 @@
         <v>5.04</v>
       </c>
       <c r="M63">
-        <v>8.78973888</v>
+        <v>8.933832960000002</v>
       </c>
       <c r="N63">
-        <v>-3.74973888</v>
+        <v>-3.893832960000002</v>
       </c>
       <c r="O63">
-        <v>-0.749947776</v>
+        <v>-0.7787665920000004</v>
       </c>
       <c r="P63">
-        <v>-2.999791104</v>
+        <v>-3.115066368000002</v>
       </c>
       <c r="Q63">
-        <v>-0.8197911040000001</v>
+        <v>-0.935066368000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1435420129898008</v>
+        <v>0.1461141712263745</v>
       </c>
       <c r="T63">
-        <v>1.648070757295999</v>
+        <v>1.691441040382736</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1146791746332287</v>
+        <v>0.1128295105262411</v>
       </c>
       <c r="W63">
-        <v>0.1777724217336477</v>
+        <v>0.1781438342863308</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5733958731661435</v>
+        <v>0.5641475526312056</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1659725623235474</v>
+        <v>0.1675225623235474</v>
       </c>
       <c r="C64">
-        <v>-20.02644745638727</v>
+        <v>-21.0546617395643</v>
       </c>
       <c r="D64">
-        <v>24.39275254361273</v>
+        <v>24.08213826043571</v>
       </c>
       <c r="E64">
-        <v>42.23120000000001</v>
+        <v>42.94880000000001</v>
       </c>
       <c r="F64">
-        <v>44.49120000000001</v>
+        <v>45.2088</v>
       </c>
       <c r="G64">
         <v>0.07199999999999999</v>
@@ -6529,37 +6529,37 @@
         <v>5.04</v>
       </c>
       <c r="M64">
-        <v>8.933832960000002</v>
+        <v>9.077927040000001</v>
       </c>
       <c r="N64">
-        <v>-3.893832960000002</v>
+        <v>-4.03792704</v>
       </c>
       <c r="O64">
-        <v>-0.7787665920000004</v>
+        <v>-0.8075854080000001</v>
       </c>
       <c r="P64">
-        <v>-3.115066368000002</v>
+        <v>-3.230341632</v>
       </c>
       <c r="Q64">
-        <v>-0.935066368000002</v>
+        <v>-1.050341632000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1461141712263745</v>
+        <v>0.1488253650433035</v>
       </c>
       <c r="T64">
-        <v>1.691441040382736</v>
+        <v>1.737155663095782</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1128295105262411</v>
+        <v>0.1110385659147135</v>
       </c>
       <c r="W64">
-        <v>0.1781438342863308</v>
+        <v>0.1785034559643255</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5641475526312056</v>
+        <v>0.5551928295735675</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1675225623235474</v>
+        <v>0.1690725623235474</v>
       </c>
       <c r="C65">
-        <v>-21.0546617395643</v>
+        <v>-22.07506484189378</v>
       </c>
       <c r="D65">
-        <v>24.08213826043571</v>
+        <v>23.77933515810622</v>
       </c>
       <c r="E65">
-        <v>42.94880000000001</v>
+        <v>43.6664</v>
       </c>
       <c r="F65">
-        <v>45.2088</v>
+        <v>45.9264</v>
       </c>
       <c r="G65">
         <v>0.07199999999999999</v>
@@ -6611,37 +6611,37 @@
         <v>5.04</v>
       </c>
       <c r="M65">
-        <v>9.077927040000001</v>
+        <v>9.222021120000001</v>
       </c>
       <c r="N65">
-        <v>-4.03792704</v>
+        <v>-4.182021120000001</v>
       </c>
       <c r="O65">
-        <v>-0.8075854080000001</v>
+        <v>-0.8364042240000003</v>
       </c>
       <c r="P65">
-        <v>-3.230341632</v>
+        <v>-3.345616896000001</v>
       </c>
       <c r="Q65">
-        <v>-1.050341632000001</v>
+        <v>-1.165616896000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1488253650433035</v>
+        <v>0.1516871807389508</v>
       </c>
       <c r="T65">
-        <v>1.737155663095782</v>
+        <v>1.785409987070665</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1110385659147135</v>
+        <v>0.1093035883222961</v>
       </c>
       <c r="W65">
-        <v>0.1785034559643255</v>
+        <v>0.178851839464883</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5551928295735675</v>
+        <v>0.5465179416114805</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1690725623235474</v>
+        <v>0.1706225623235474</v>
       </c>
       <c r="C66">
-        <v>-22.07506484189378</v>
+        <v>-23.08794775236254</v>
       </c>
       <c r="D66">
-        <v>23.77933515810622</v>
+        <v>23.48405224763746</v>
       </c>
       <c r="E66">
-        <v>43.6664</v>
+        <v>44.38400000000001</v>
       </c>
       <c r="F66">
-        <v>45.9264</v>
+        <v>46.64400000000001</v>
       </c>
       <c r="G66">
         <v>0.07199999999999999</v>
@@ -6693,37 +6693,37 @@
         <v>5.04</v>
       </c>
       <c r="M66">
-        <v>9.222021120000001</v>
+        <v>9.366115200000001</v>
       </c>
       <c r="N66">
-        <v>-4.182021120000001</v>
+        <v>-4.326115200000001</v>
       </c>
       <c r="O66">
-        <v>-0.8364042240000003</v>
+        <v>-0.8652230400000003</v>
       </c>
       <c r="P66">
-        <v>-3.345616896000001</v>
+        <v>-3.460892160000001</v>
       </c>
       <c r="Q66">
-        <v>-1.165616896000001</v>
+        <v>-1.280892160000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1516871807389508</v>
+        <v>0.1547125287600637</v>
       </c>
       <c r="T66">
-        <v>1.785409987070665</v>
+        <v>1.83642170098697</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1093035883222961</v>
+        <v>0.1076219946557992</v>
       </c>
       <c r="W66">
-        <v>0.178851839464883</v>
+        <v>0.1791895034731155</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5465179416114805</v>
+        <v>0.5381099732789961</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1706225623235474</v>
+        <v>0.1721725623235474</v>
       </c>
       <c r="C67">
-        <v>-23.08794775236254</v>
+        <v>-24.09358718366443</v>
       </c>
       <c r="D67">
-        <v>23.48405224763746</v>
+        <v>23.19601281633557</v>
       </c>
       <c r="E67">
-        <v>44.38400000000001</v>
+        <v>45.1016</v>
       </c>
       <c r="F67">
-        <v>46.64400000000001</v>
+        <v>47.3616</v>
       </c>
       <c r="G67">
         <v>0.07199999999999999</v>
@@ -6775,37 +6775,37 @@
         <v>5.04</v>
       </c>
       <c r="M67">
-        <v>9.366115200000001</v>
+        <v>9.510209280000002</v>
       </c>
       <c r="N67">
-        <v>-4.326115200000001</v>
+        <v>-4.470209280000002</v>
       </c>
       <c r="O67">
-        <v>-0.8652230400000003</v>
+        <v>-0.8940418560000003</v>
       </c>
       <c r="P67">
-        <v>-3.460892160000001</v>
+        <v>-3.576167424000001</v>
       </c>
       <c r="Q67">
-        <v>-1.280892160000001</v>
+        <v>-1.396167424000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1547125287600637</v>
+        <v>0.1579158384294774</v>
       </c>
       <c r="T67">
-        <v>1.83642170098697</v>
+        <v>1.890434103957175</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1076219946557992</v>
+        <v>0.1059913583731356</v>
       </c>
       <c r="W67">
-        <v>0.1791895034731155</v>
+        <v>0.1795169352386744</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5381099732789961</v>
+        <v>0.529956791865678</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1721725623235474</v>
+        <v>0.1737225623235474</v>
       </c>
       <c r="C68">
-        <v>-24.09358718366443</v>
+        <v>-25.0922464371086</v>
       </c>
       <c r="D68">
-        <v>23.19601281633557</v>
+        <v>22.91495356289141</v>
       </c>
       <c r="E68">
-        <v>45.1016</v>
+        <v>45.81920000000001</v>
       </c>
       <c r="F68">
-        <v>47.3616</v>
+        <v>48.07920000000001</v>
       </c>
       <c r="G68">
         <v>0.07199999999999999</v>
@@ -6857,37 +6857,37 @@
         <v>5.04</v>
       </c>
       <c r="M68">
-        <v>9.510209280000002</v>
+        <v>9.654303360000002</v>
       </c>
       <c r="N68">
-        <v>-4.470209280000002</v>
+        <v>-4.614303360000002</v>
       </c>
       <c r="O68">
-        <v>-0.8940418560000003</v>
+        <v>-0.9228606720000004</v>
       </c>
       <c r="P68">
-        <v>-3.576167424000001</v>
+        <v>-3.691442688000001</v>
       </c>
       <c r="Q68">
-        <v>-1.396167424000001</v>
+        <v>-1.511442688000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1579158384294774</v>
+        <v>0.1613132880788555</v>
       </c>
       <c r="T68">
-        <v>1.890434103957175</v>
+        <v>1.947719985895271</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1059913583731356</v>
+        <v>0.1044093978004022</v>
       </c>
       <c r="W68">
-        <v>0.1795169352386744</v>
+        <v>0.1798345929216792</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.529956791865678</v>
+        <v>0.5220469890020112</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1737225623235474</v>
+        <v>0.1752725623235474</v>
       </c>
       <c r="C69">
-        <v>-25.0922464371086</v>
+        <v>-26.0841762054013</v>
       </c>
       <c r="D69">
-        <v>22.91495356289141</v>
+        <v>22.64062379459871</v>
       </c>
       <c r="E69">
-        <v>45.81920000000001</v>
+        <v>46.53680000000001</v>
       </c>
       <c r="F69">
-        <v>48.07920000000001</v>
+        <v>48.7968</v>
       </c>
       <c r="G69">
         <v>0.07199999999999999</v>
@@ -6939,37 +6939,37 @@
         <v>5.04</v>
       </c>
       <c r="M69">
-        <v>9.654303360000002</v>
+        <v>9.79839744</v>
       </c>
       <c r="N69">
-        <v>-4.614303360000002</v>
+        <v>-4.75839744</v>
       </c>
       <c r="O69">
-        <v>-0.9228606720000004</v>
+        <v>-0.9516794880000001</v>
       </c>
       <c r="P69">
-        <v>-3.691442688000001</v>
+        <v>-3.806717952000001</v>
       </c>
       <c r="Q69">
-        <v>-1.511442688000002</v>
+        <v>-1.626717952000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1613132880788555</v>
+        <v>0.1649230783313197</v>
       </c>
       <c r="T69">
-        <v>1.947719985895271</v>
+        <v>2.008586235454499</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1044093978004022</v>
+        <v>0.1028739654798081</v>
       </c>
       <c r="W69">
-        <v>0.1798345929216792</v>
+        <v>0.1801429077316545</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5220469890020112</v>
+        <v>0.5143698273990405</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1752725623235474</v>
+        <v>0.1768225623235474</v>
       </c>
       <c r="C70">
-        <v>-26.0841762054013</v>
+        <v>-27.06961531844635</v>
       </c>
       <c r="D70">
-        <v>22.64062379459871</v>
+        <v>22.37278468155366</v>
       </c>
       <c r="E70">
-        <v>46.53680000000001</v>
+        <v>47.25440000000001</v>
       </c>
       <c r="F70">
-        <v>48.7968</v>
+        <v>49.51440000000001</v>
       </c>
       <c r="G70">
         <v>0.07199999999999999</v>
@@ -7021,37 +7021,37 @@
         <v>5.04</v>
       </c>
       <c r="M70">
-        <v>9.79839744</v>
+        <v>9.942491520000003</v>
       </c>
       <c r="N70">
-        <v>-4.75839744</v>
+        <v>-4.902491520000003</v>
       </c>
       <c r="O70">
-        <v>-0.9516794880000001</v>
+        <v>-0.9804983040000006</v>
       </c>
       <c r="P70">
-        <v>-3.806717952000001</v>
+        <v>-3.921993216000002</v>
       </c>
       <c r="Q70">
-        <v>-1.626717952000001</v>
+        <v>-1.741993216000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1649230783313197</v>
+        <v>0.1687657582774913</v>
       </c>
       <c r="T70">
-        <v>2.008586235454499</v>
+        <v>2.073379339823999</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1028739654798081</v>
+        <v>0.1013830384438688</v>
       </c>
       <c r="W70">
-        <v>0.1801429077316545</v>
+        <v>0.1804422858804711</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5143698273990405</v>
+        <v>0.5069151922193441</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1768225623235474</v>
+        <v>0.203298141365413</v>
       </c>
       <c r="C71">
-        <v>-27.06961531844635</v>
+        <v>-31.54810052056971</v>
       </c>
       <c r="D71">
-        <v>22.37278468155366</v>
+        <v>18.6118994794303</v>
       </c>
       <c r="E71">
-        <v>47.25440000000001</v>
+        <v>47.97200000000001</v>
       </c>
       <c r="F71">
-        <v>49.51440000000001</v>
+        <v>50.23200000000001</v>
       </c>
       <c r="G71">
         <v>0.07199999999999999</v>
@@ -7103,45 +7103,45 @@
         <v>5.04</v>
       </c>
       <c r="M71">
-        <v>9.942491520000003</v>
+        <v>11.8447056</v>
       </c>
       <c r="N71">
-        <v>-4.902491520000003</v>
+        <v>-6.804705600000003</v>
       </c>
       <c r="O71">
-        <v>-0.9804983040000006</v>
+        <v>-1.360941120000001</v>
       </c>
       <c r="P71">
-        <v>-3.921993216000002</v>
+        <v>-5.443764480000002</v>
       </c>
       <c r="Q71">
-        <v>-1.741993216000002</v>
+        <v>-3.263764480000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1687657582774913</v>
+        <v>0.1742832136929598</v>
       </c>
       <c r="T71">
-        <v>2.073379339823999</v>
+        <v>2.166411564624473</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1013830384438688</v>
+        <v>0.08510131311326133</v>
       </c>
       <c r="W71">
-        <v>0.1804422858804711</v>
+        <v>0.215733110367893</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5069151922193441</v>
+        <v>0.4255065655663066</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.203298141365413</v>
+        <v>0.205198141365413</v>
       </c>
       <c r="C72">
-        <v>-31.54810052056971</v>
+        <v>-32.48755134460065</v>
       </c>
       <c r="D72">
-        <v>18.6118994794303</v>
+        <v>18.39004865539936</v>
       </c>
       <c r="E72">
-        <v>47.97200000000001</v>
+        <v>48.68960000000001</v>
       </c>
       <c r="F72">
-        <v>50.23200000000001</v>
+        <v>50.94960000000001</v>
       </c>
       <c r="G72">
         <v>0.07199999999999999</v>
@@ -7185,37 +7185,37 @@
         <v>5.04</v>
       </c>
       <c r="M72">
-        <v>11.8447056</v>
+        <v>12.01391568</v>
       </c>
       <c r="N72">
-        <v>-6.804705600000003</v>
+        <v>-6.973915680000004</v>
       </c>
       <c r="O72">
-        <v>-1.360941120000001</v>
+        <v>-1.394783136000001</v>
       </c>
       <c r="P72">
-        <v>-5.443764480000002</v>
+        <v>-5.579132544000003</v>
       </c>
       <c r="Q72">
-        <v>-3.263764480000003</v>
+        <v>-3.399132544000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1742832136929598</v>
+        <v>0.1787136693375446</v>
       </c>
       <c r="T72">
-        <v>2.166411564624473</v>
+        <v>2.241115411680489</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08510131311326133</v>
+        <v>0.08390270306941257</v>
       </c>
       <c r="W72">
-        <v>0.215733110367893</v>
+        <v>0.2160157426162325</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4255065655663066</v>
+        <v>0.4195135153470628</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.205198141365413</v>
+        <v>0.207098141365413</v>
       </c>
       <c r="C73">
-        <v>-32.48755134460065</v>
+        <v>-33.42177561658219</v>
       </c>
       <c r="D73">
-        <v>18.39004865539936</v>
+        <v>18.17342438341781</v>
       </c>
       <c r="E73">
-        <v>48.68960000000001</v>
+        <v>49.4072</v>
       </c>
       <c r="F73">
-        <v>50.9496</v>
+        <v>51.6672</v>
       </c>
       <c r="G73">
         <v>0.07199999999999999</v>
@@ -7267,37 +7267,37 @@
         <v>5.04</v>
       </c>
       <c r="M73">
-        <v>12.01391568</v>
+        <v>12.18312576</v>
       </c>
       <c r="N73">
-        <v>-6.973915680000002</v>
+        <v>-7.143125760000001</v>
       </c>
       <c r="O73">
-        <v>-1.394783136</v>
+        <v>-1.428625152</v>
       </c>
       <c r="P73">
-        <v>-5.579132544000002</v>
+        <v>-5.714500608000001</v>
       </c>
       <c r="Q73">
-        <v>-3.399132544000002</v>
+        <v>-3.534500608000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1787136693375446</v>
+        <v>0.1834605860995997</v>
       </c>
       <c r="T73">
-        <v>2.241115411680489</v>
+        <v>2.321155247811935</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08390270306941258</v>
+        <v>0.08273738774900408</v>
       </c>
       <c r="W73">
-        <v>0.2160157426162325</v>
+        <v>0.2162905239687848</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4195135153470628</v>
+        <v>0.4136869387450204</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.207098141365413</v>
+        <v>0.208998141365413</v>
       </c>
       <c r="C74">
-        <v>-33.42177561658219</v>
+        <v>-34.35095588360974</v>
       </c>
       <c r="D74">
-        <v>18.17342438341781</v>
+        <v>17.96184411639027</v>
       </c>
       <c r="E74">
-        <v>49.4072</v>
+        <v>50.12480000000001</v>
       </c>
       <c r="F74">
-        <v>51.6672</v>
+        <v>52.38480000000001</v>
       </c>
       <c r="G74">
         <v>0.07199999999999999</v>
@@ -7349,37 +7349,37 @@
         <v>5.04</v>
       </c>
       <c r="M74">
-        <v>12.18312576</v>
+        <v>12.35233584</v>
       </c>
       <c r="N74">
-        <v>-7.143125760000001</v>
+        <v>-7.312335840000002</v>
       </c>
       <c r="O74">
-        <v>-1.428625152</v>
+        <v>-1.462467168000001</v>
       </c>
       <c r="P74">
-        <v>-5.714500608000001</v>
+        <v>-5.849868672000001</v>
       </c>
       <c r="Q74">
-        <v>-3.534500608000001</v>
+        <v>-3.669868672000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1834605860995997</v>
+        <v>0.1885591263255108</v>
       </c>
       <c r="T74">
-        <v>2.321155247811935</v>
+        <v>2.407123960693858</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08273738774900408</v>
+        <v>0.08160399887573004</v>
       </c>
       <c r="W74">
-        <v>0.2162905239687848</v>
+        <v>0.2165577770651029</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4136869387450204</v>
+        <v>0.4080199943786502</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.208998141365413</v>
+        <v>0.210898141365413</v>
       </c>
       <c r="C75">
-        <v>-34.35095588360974</v>
+        <v>-35.27526628954706</v>
       </c>
       <c r="D75">
-        <v>17.96184411639027</v>
+        <v>17.75513371045295</v>
       </c>
       <c r="E75">
-        <v>50.12480000000001</v>
+        <v>50.8424</v>
       </c>
       <c r="F75">
-        <v>52.38480000000001</v>
+        <v>53.1024</v>
       </c>
       <c r="G75">
         <v>0.07199999999999999</v>
@@ -7431,37 +7431,37 @@
         <v>5.04</v>
       </c>
       <c r="M75">
-        <v>12.35233584</v>
+        <v>12.52154592</v>
       </c>
       <c r="N75">
-        <v>-7.312335840000002</v>
+        <v>-7.481545920000001</v>
       </c>
       <c r="O75">
-        <v>-1.462467168000001</v>
+        <v>-1.496309184</v>
       </c>
       <c r="P75">
-        <v>-5.849868672000001</v>
+        <v>-5.985236736000001</v>
       </c>
       <c r="Q75">
-        <v>-3.669868672000002</v>
+        <v>-3.805236736000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1885591263255108</v>
+        <v>0.1940498619534151</v>
       </c>
       <c r="T75">
-        <v>2.407123960693858</v>
+        <v>2.499705651489776</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08160399887573004</v>
+        <v>0.08050124213416612</v>
       </c>
       <c r="W75">
-        <v>0.2165577770651029</v>
+        <v>0.2168178071047636</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4080199943786502</v>
+        <v>0.4025062106708306</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.210898141365413</v>
+        <v>0.212798141365413</v>
       </c>
       <c r="C76">
-        <v>-35.27526628954706</v>
+        <v>-36.19487305305974</v>
       </c>
       <c r="D76">
-        <v>17.75513371045295</v>
+        <v>17.55312694694027</v>
       </c>
       <c r="E76">
-        <v>50.8424</v>
+        <v>51.56000000000001</v>
       </c>
       <c r="F76">
-        <v>53.1024</v>
+        <v>53.82000000000001</v>
       </c>
       <c r="G76">
         <v>0.07199999999999999</v>
@@ -7513,37 +7513,37 @@
         <v>5.04</v>
       </c>
       <c r="M76">
-        <v>12.52154592</v>
+        <v>12.690756</v>
       </c>
       <c r="N76">
-        <v>-7.481545920000001</v>
+        <v>-7.650756000000002</v>
       </c>
       <c r="O76">
-        <v>-1.496309184</v>
+        <v>-1.530151200000001</v>
       </c>
       <c r="P76">
-        <v>-5.985236736000001</v>
+        <v>-6.120604800000002</v>
       </c>
       <c r="Q76">
-        <v>-3.805236736000001</v>
+        <v>-3.940604800000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1940498619534151</v>
+        <v>0.1999798564315517</v>
       </c>
       <c r="T76">
-        <v>2.499705651489776</v>
+        <v>2.599693877549367</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08050124213416612</v>
+        <v>0.07942789223904391</v>
       </c>
       <c r="W76">
-        <v>0.2168178071047636</v>
+        <v>0.2170709030100335</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4025062106708306</v>
+        <v>0.3971394611952195</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.212798141365413</v>
+        <v>0.214698141365413</v>
       </c>
       <c r="C77">
-        <v>-36.19487305305974</v>
+        <v>-37.10993491338319</v>
       </c>
       <c r="D77">
-        <v>17.55312694694027</v>
+        <v>17.35566508661682</v>
       </c>
       <c r="E77">
-        <v>51.56000000000001</v>
+        <v>52.27760000000001</v>
       </c>
       <c r="F77">
-        <v>53.82000000000001</v>
+        <v>54.5376</v>
       </c>
       <c r="G77">
         <v>0.07199999999999999</v>
@@ -7595,37 +7595,37 @@
         <v>5.04</v>
       </c>
       <c r="M77">
-        <v>12.690756</v>
+        <v>12.85996608</v>
       </c>
       <c r="N77">
-        <v>-7.650756000000002</v>
+        <v>-7.819966080000001</v>
       </c>
       <c r="O77">
-        <v>-1.530151200000001</v>
+        <v>-1.563993216</v>
       </c>
       <c r="P77">
-        <v>-6.120604800000002</v>
+        <v>-6.255972864000001</v>
       </c>
       <c r="Q77">
-        <v>-3.940604800000002</v>
+        <v>-4.075972864000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1999798564315517</v>
+        <v>0.2064040171161997</v>
       </c>
       <c r="T77">
-        <v>2.599693877549367</v>
+        <v>2.708014455780591</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07942789223904391</v>
+        <v>0.07838278839379334</v>
       </c>
       <c r="W77">
-        <v>0.2170709030100335</v>
+        <v>0.2173173384967435</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3971394611952195</v>
+        <v>0.3919139419689667</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.214698141365413</v>
+        <v>0.216598141365413</v>
       </c>
       <c r="C78">
-        <v>-37.10993491338319</v>
+        <v>-38.02060354633758</v>
       </c>
       <c r="D78">
-        <v>17.35566508661682</v>
+        <v>17.16259645366243</v>
       </c>
       <c r="E78">
-        <v>52.27760000000001</v>
+        <v>52.9952</v>
       </c>
       <c r="F78">
-        <v>54.5376</v>
+        <v>55.2552</v>
       </c>
       <c r="G78">
         <v>0.07199999999999999</v>
@@ -7677,37 +7677,37 @@
         <v>5.04</v>
       </c>
       <c r="M78">
-        <v>12.85996608</v>
+        <v>13.02917616</v>
       </c>
       <c r="N78">
-        <v>-7.819966080000001</v>
+        <v>-7.98917616</v>
       </c>
       <c r="O78">
-        <v>-1.563993216</v>
+        <v>-1.597835232</v>
       </c>
       <c r="P78">
-        <v>-6.255972864000001</v>
+        <v>-6.391340928</v>
       </c>
       <c r="Q78">
-        <v>-4.075972864000001</v>
+        <v>-4.211340928</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2064040171161997</v>
+        <v>0.213386800469078</v>
       </c>
       <c r="T78">
-        <v>2.708014455780591</v>
+        <v>2.825754214727573</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07838278839379334</v>
+        <v>0.07736483010296485</v>
       </c>
       <c r="W78">
-        <v>0.2173173384967435</v>
+        <v>0.2175573730617209</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3919139419689667</v>
+        <v>0.3868241505148242</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.216598141365413</v>
+        <v>0.218498141365413</v>
       </c>
       <c r="C79">
-        <v>-38.02060354633758</v>
+        <v>-38.92702395288128</v>
       </c>
       <c r="D79">
-        <v>17.16259645366243</v>
+        <v>16.97377604711873</v>
       </c>
       <c r="E79">
-        <v>52.9952</v>
+        <v>53.71280000000001</v>
       </c>
       <c r="F79">
-        <v>55.2552</v>
+        <v>55.97280000000001</v>
       </c>
       <c r="G79">
         <v>0.07199999999999999</v>
@@ -7759,37 +7759,37 @@
         <v>5.04</v>
       </c>
       <c r="M79">
-        <v>13.02917616</v>
+        <v>13.19838624</v>
       </c>
       <c r="N79">
-        <v>-7.98917616</v>
+        <v>-8.158386240000002</v>
       </c>
       <c r="O79">
-        <v>-1.597835232</v>
+        <v>-1.631677248000001</v>
       </c>
       <c r="P79">
-        <v>-6.391340928</v>
+        <v>-6.526708992000001</v>
       </c>
       <c r="Q79">
-        <v>-4.211340928</v>
+        <v>-4.346708992000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.213386800469078</v>
+        <v>0.2210043823085815</v>
       </c>
       <c r="T79">
-        <v>2.825754214727573</v>
+        <v>2.954197588124281</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07736483010296485</v>
+        <v>0.07637297330677299</v>
       </c>
       <c r="W79">
-        <v>0.2175573730617209</v>
+        <v>0.217791252894263</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3868241505148242</v>
+        <v>0.3818648665338649</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.218498141365413</v>
+        <v>0.220398141365413</v>
       </c>
       <c r="C80">
-        <v>-38.92702395288128</v>
+        <v>-39.82933482229443</v>
       </c>
       <c r="D80">
-        <v>16.97377604711873</v>
+        <v>16.78906517770557</v>
       </c>
       <c r="E80">
-        <v>53.71280000000001</v>
+        <v>54.43040000000001</v>
       </c>
       <c r="F80">
-        <v>55.97280000000001</v>
+        <v>56.6904</v>
       </c>
       <c r="G80">
         <v>0.07199999999999999</v>
@@ -7841,37 +7841,37 @@
         <v>5.04</v>
       </c>
       <c r="M80">
-        <v>13.19838624</v>
+        <v>13.36759632</v>
       </c>
       <c r="N80">
-        <v>-8.158386240000002</v>
+        <v>-8.327596320000001</v>
       </c>
       <c r="O80">
-        <v>-1.631677248000001</v>
+        <v>-1.665519264</v>
       </c>
       <c r="P80">
-        <v>-6.526708992000001</v>
+        <v>-6.662077056000001</v>
       </c>
       <c r="Q80">
-        <v>-4.346708992000002</v>
+        <v>-4.482077056000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2210043823085815</v>
+        <v>0.2293474481327997</v>
       </c>
       <c r="T80">
-        <v>2.954197588124281</v>
+        <v>3.094873663749247</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07637297330677299</v>
+        <v>0.07540622680921889</v>
       </c>
       <c r="W80">
-        <v>0.217791252894263</v>
+        <v>0.2180192117183862</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3818648665338649</v>
+        <v>0.3770311340460946</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.220398141365413</v>
+        <v>0.222298141365413</v>
       </c>
       <c r="C81">
-        <v>-39.82933482229443</v>
+        <v>-40.72766887190461</v>
       </c>
       <c r="D81">
-        <v>16.78906517770557</v>
+        <v>16.60833112809539</v>
       </c>
       <c r="E81">
-        <v>54.43040000000001</v>
+        <v>55.14800000000001</v>
       </c>
       <c r="F81">
-        <v>56.6904</v>
+        <v>57.40800000000001</v>
       </c>
       <c r="G81">
         <v>0.07199999999999999</v>
@@ -7923,37 +7923,37 @@
         <v>5.04</v>
       </c>
       <c r="M81">
-        <v>13.36759632</v>
+        <v>13.5368064</v>
       </c>
       <c r="N81">
-        <v>-8.327596320000001</v>
+        <v>-8.496806400000004</v>
       </c>
       <c r="O81">
-        <v>-1.665519264</v>
+        <v>-1.699361280000001</v>
       </c>
       <c r="P81">
-        <v>-6.662077056000001</v>
+        <v>-6.797445120000003</v>
       </c>
       <c r="Q81">
-        <v>-4.482077056000001</v>
+        <v>-4.617445120000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2293474481327997</v>
+        <v>0.2385248205394397</v>
       </c>
       <c r="T81">
-        <v>3.094873663749247</v>
+        <v>3.249617346936709</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07540622680921889</v>
+        <v>0.07446364897410367</v>
       </c>
       <c r="W81">
-        <v>0.2180192117183862</v>
+        <v>0.2182414715719064</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3770311340460946</v>
+        <v>0.3723182448705182</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.222298141365413</v>
+        <v>0.224198141365413</v>
       </c>
       <c r="C82">
-        <v>-40.72766887190461</v>
+        <v>-41.6221531651033</v>
       </c>
       <c r="D82">
-        <v>16.60833112809539</v>
+        <v>16.4314468348967</v>
       </c>
       <c r="E82">
-        <v>55.14800000000001</v>
+        <v>55.86560000000001</v>
       </c>
       <c r="F82">
-        <v>57.40800000000001</v>
+        <v>58.12560000000001</v>
       </c>
       <c r="G82">
         <v>0.07199999999999999</v>
@@ -8005,37 +8005,37 @@
         <v>5.04</v>
       </c>
       <c r="M82">
-        <v>13.5368064</v>
+        <v>13.70601648</v>
       </c>
       <c r="N82">
-        <v>-8.496806400000004</v>
+        <v>-8.666016480000003</v>
       </c>
       <c r="O82">
-        <v>-1.699361280000001</v>
+        <v>-1.733203296000001</v>
       </c>
       <c r="P82">
-        <v>-6.797445120000003</v>
+        <v>-6.932813184000002</v>
       </c>
       <c r="Q82">
-        <v>-4.617445120000004</v>
+        <v>-4.752813184000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2385248205394397</v>
+        <v>0.2486682321467786</v>
       </c>
       <c r="T82">
-        <v>3.249617346936709</v>
+        <v>3.420649838880747</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07446364897410367</v>
+        <v>0.0735443446657814</v>
       </c>
       <c r="W82">
-        <v>0.2182414715719064</v>
+        <v>0.2184582435278088</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3723182448705182</v>
+        <v>0.3677217233289068</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.224198141365413</v>
+        <v>0.2260981413654131</v>
       </c>
       <c r="C83">
-        <v>-41.6221531651033</v>
+        <v>-42.51290940925466</v>
       </c>
       <c r="D83">
-        <v>16.4314468348967</v>
+        <v>16.25829059074535</v>
       </c>
       <c r="E83">
-        <v>55.86560000000001</v>
+        <v>56.58320000000001</v>
       </c>
       <c r="F83">
-        <v>58.12560000000001</v>
+        <v>58.84320000000001</v>
       </c>
       <c r="G83">
         <v>0.07199999999999999</v>
@@ -8087,37 +8087,37 @@
         <v>5.04</v>
       </c>
       <c r="M83">
-        <v>13.70601648</v>
+        <v>13.87522656</v>
       </c>
       <c r="N83">
-        <v>-8.666016480000003</v>
+        <v>-8.835226560000002</v>
       </c>
       <c r="O83">
-        <v>-1.733203296000001</v>
+        <v>-1.767045312</v>
       </c>
       <c r="P83">
-        <v>-6.932813184000002</v>
+        <v>-7.068181248000002</v>
       </c>
       <c r="Q83">
-        <v>-4.752813184000003</v>
+        <v>-4.888181248000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2486682321467786</v>
+        <v>0.2599386894882663</v>
       </c>
       <c r="T83">
-        <v>3.420649838880747</v>
+        <v>3.610685941040789</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0735443446657814</v>
+        <v>0.07264746241375968</v>
       </c>
       <c r="W83">
-        <v>0.2184582435278088</v>
+        <v>0.2186697283628355</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3677217233289068</v>
+        <v>0.3632373120687984</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2260981413654131</v>
+        <v>0.227998141365413</v>
       </c>
       <c r="C84">
-        <v>-42.51290940925466</v>
+        <v>-43.40005423496427</v>
       </c>
       <c r="D84">
-        <v>16.25829059074535</v>
+        <v>16.08874576503574</v>
       </c>
       <c r="E84">
-        <v>56.58320000000001</v>
+        <v>57.30080000000001</v>
       </c>
       <c r="F84">
-        <v>58.84320000000001</v>
+        <v>59.56080000000001</v>
       </c>
       <c r="G84">
         <v>0.07199999999999999</v>
@@ -8169,37 +8169,37 @@
         <v>5.04</v>
       </c>
       <c r="M84">
-        <v>13.87522656</v>
+        <v>14.04443664</v>
       </c>
       <c r="N84">
-        <v>-8.835226560000002</v>
+        <v>-9.004436640000002</v>
       </c>
       <c r="O84">
-        <v>-1.767045312</v>
+        <v>-1.800887328</v>
       </c>
       <c r="P84">
-        <v>-7.068181248000002</v>
+        <v>-7.203549312000002</v>
       </c>
       <c r="Q84">
-        <v>-4.888181248000002</v>
+        <v>-5.023549312000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2599386894882663</v>
+        <v>0.2725350829875761</v>
       </c>
       <c r="T84">
-        <v>3.610685941040789</v>
+        <v>3.823079231690247</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07264746241375968</v>
+        <v>0.0717721917822686</v>
       </c>
       <c r="W84">
-        <v>0.2186697283628355</v>
+        <v>0.2188761171777411</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3632373120687984</v>
+        <v>0.358860958911343</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.227998141365413</v>
+        <v>0.2298981413654131</v>
       </c>
       <c r="C85">
-        <v>-43.40005423496427</v>
+        <v>-44.28369945805478</v>
       </c>
       <c r="D85">
-        <v>16.08874576503574</v>
+        <v>15.92270054194523</v>
       </c>
       <c r="E85">
-        <v>57.30080000000001</v>
+        <v>58.01840000000001</v>
       </c>
       <c r="F85">
-        <v>59.56080000000001</v>
+        <v>60.27840000000001</v>
       </c>
       <c r="G85">
         <v>0.07199999999999999</v>
@@ -8251,37 +8251,37 @@
         <v>5.04</v>
       </c>
       <c r="M85">
-        <v>14.04443664</v>
+        <v>14.21364672</v>
       </c>
       <c r="N85">
-        <v>-9.004436640000002</v>
+        <v>-9.173646720000004</v>
       </c>
       <c r="O85">
-        <v>-1.800887328</v>
+        <v>-1.834729344000001</v>
       </c>
       <c r="P85">
-        <v>-7.203549312000002</v>
+        <v>-7.338917376000003</v>
       </c>
       <c r="Q85">
-        <v>-5.023549312000002</v>
+        <v>-5.158917376000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2725350829875761</v>
+        <v>0.2867060256742997</v>
       </c>
       <c r="T85">
-        <v>3.823079231690247</v>
+        <v>4.062021683670888</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0717721917822686</v>
+        <v>0.07091776092771777</v>
       </c>
       <c r="W85">
-        <v>0.2188761171777411</v>
+        <v>0.2190775919732442</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.358860958911343</v>
+        <v>0.3545888046385888</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.229898141365413</v>
+        <v>0.231798141365413</v>
       </c>
       <c r="C86">
-        <v>-44.28369945805478</v>
+        <v>-45.16395232548457</v>
       </c>
       <c r="D86">
-        <v>15.92270054194523</v>
+        <v>15.76004767451543</v>
       </c>
       <c r="E86">
-        <v>58.01840000000001</v>
+        <v>58.736</v>
       </c>
       <c r="F86">
-        <v>60.2784</v>
+        <v>60.996</v>
       </c>
       <c r="G86">
         <v>0.07199999999999999</v>
@@ -8333,37 +8333,37 @@
         <v>5.04</v>
       </c>
       <c r="M86">
-        <v>14.21364672</v>
+        <v>14.3828568</v>
       </c>
       <c r="N86">
-        <v>-9.173646720000001</v>
+        <v>-9.3428568</v>
       </c>
       <c r="O86">
-        <v>-1.834729344</v>
+        <v>-1.86857136</v>
       </c>
       <c r="P86">
-        <v>-7.338917376</v>
+        <v>-7.47428544</v>
       </c>
       <c r="Q86">
-        <v>-5.158917376000001</v>
+        <v>-5.29428544</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2867060256742995</v>
+        <v>0.3027664273859195</v>
       </c>
       <c r="T86">
-        <v>4.062021683670886</v>
+        <v>4.332823129248945</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07091776092771777</v>
+        <v>0.07008343432856816</v>
       </c>
       <c r="W86">
-        <v>0.2190775919732442</v>
+        <v>0.2192743261853236</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3545888046385889</v>
+        <v>0.3504171716428408</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.231798141365413</v>
+        <v>0.233698141365413</v>
       </c>
       <c r="C87">
-        <v>-45.16395232548457</v>
+        <v>-46.04091574634644</v>
       </c>
       <c r="D87">
-        <v>15.76004767451543</v>
+        <v>15.60068425365357</v>
       </c>
       <c r="E87">
-        <v>58.736</v>
+        <v>59.45360000000001</v>
       </c>
       <c r="F87">
-        <v>60.996</v>
+        <v>61.71360000000001</v>
       </c>
       <c r="G87">
         <v>0.07199999999999999</v>
@@ -8415,37 +8415,37 @@
         <v>5.04</v>
       </c>
       <c r="M87">
-        <v>14.3828568</v>
+        <v>14.55206688</v>
       </c>
       <c r="N87">
-        <v>-9.3428568</v>
+        <v>-9.512066880000003</v>
       </c>
       <c r="O87">
-        <v>-1.86857136</v>
+        <v>-1.902413376000001</v>
       </c>
       <c r="P87">
-        <v>-7.47428544</v>
+        <v>-7.609653504000002</v>
       </c>
       <c r="Q87">
-        <v>-5.29428544</v>
+        <v>-5.429653504000003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3027664273859195</v>
+        <v>0.3211211721991994</v>
       </c>
       <c r="T87">
-        <v>4.332823129248945</v>
+        <v>4.642310495623869</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07008343432856816</v>
+        <v>0.0692685106735848</v>
       </c>
       <c r="W87">
-        <v>0.2192743261853236</v>
+        <v>0.2194664851831687</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3504171716428408</v>
+        <v>0.346342553367924</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.233698141365413</v>
+        <v>0.235598141365413</v>
       </c>
       <c r="C88">
-        <v>-46.04091574634644</v>
+        <v>-46.91468850899153</v>
       </c>
       <c r="D88">
-        <v>15.60068425365357</v>
+        <v>15.44451149100847</v>
       </c>
       <c r="E88">
-        <v>59.45360000000001</v>
+        <v>60.17120000000001</v>
       </c>
       <c r="F88">
-        <v>61.71360000000001</v>
+        <v>62.4312</v>
       </c>
       <c r="G88">
         <v>0.07199999999999999</v>
@@ -8497,37 +8497,37 @@
         <v>5.04</v>
       </c>
       <c r="M88">
-        <v>14.55206688</v>
+        <v>14.72127696</v>
       </c>
       <c r="N88">
-        <v>-9.512066880000003</v>
+        <v>-9.681276960000002</v>
       </c>
       <c r="O88">
-        <v>-1.902413376000001</v>
+        <v>-1.936255392000001</v>
       </c>
       <c r="P88">
-        <v>-7.609653504000002</v>
+        <v>-7.745021568000001</v>
       </c>
       <c r="Q88">
-        <v>-5.429653504000003</v>
+        <v>-5.565021568000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3211211721991994</v>
+        <v>0.3422997239068302</v>
       </c>
       <c r="T88">
-        <v>4.642310495623869</v>
+        <v>4.999411302979551</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0692685106735848</v>
+        <v>0.06847232089572751</v>
       </c>
       <c r="W88">
-        <v>0.2194664851831687</v>
+        <v>0.2196542267327874</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.346342553367924</v>
+        <v>0.3423616044786375</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.235598141365413</v>
+        <v>0.237498141365413</v>
       </c>
       <c r="C89">
-        <v>-46.91468850899153</v>
+        <v>-47.78536548524129</v>
       </c>
       <c r="D89">
-        <v>15.44451149100847</v>
+        <v>15.29143451475871</v>
       </c>
       <c r="E89">
-        <v>60.17120000000001</v>
+        <v>60.8888</v>
       </c>
       <c r="F89">
-        <v>62.4312</v>
+        <v>63.1488</v>
       </c>
       <c r="G89">
         <v>0.07199999999999999</v>
@@ -8579,37 +8579,37 @@
         <v>5.04</v>
       </c>
       <c r="M89">
-        <v>14.72127696</v>
+        <v>14.89048704</v>
       </c>
       <c r="N89">
-        <v>-9.681276960000002</v>
+        <v>-9.850487040000001</v>
       </c>
       <c r="O89">
-        <v>-1.936255392000001</v>
+        <v>-1.970097408</v>
       </c>
       <c r="P89">
-        <v>-7.745021568000001</v>
+        <v>-7.880389632000001</v>
       </c>
       <c r="Q89">
-        <v>-5.565021568000001</v>
+        <v>-5.700389632000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3422997239068302</v>
+        <v>0.3670080342323995</v>
       </c>
       <c r="T89">
-        <v>4.999411302979551</v>
+        <v>5.416028911561182</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06847232089572751</v>
+        <v>0.06769422634009424</v>
       </c>
       <c r="W89">
-        <v>0.2196542267327874</v>
+        <v>0.2198377014290058</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3423616044786375</v>
+        <v>0.3384711317004713</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.237498141365413</v>
+        <v>0.239398141365413</v>
       </c>
       <c r="C90">
-        <v>-47.78536548524129</v>
+        <v>-48.65303782257435</v>
       </c>
       <c r="D90">
-        <v>15.29143451475871</v>
+        <v>15.14136217742566</v>
       </c>
       <c r="E90">
-        <v>60.8888</v>
+        <v>61.60640000000001</v>
       </c>
       <c r="F90">
-        <v>63.1488</v>
+        <v>63.86640000000001</v>
       </c>
       <c r="G90">
         <v>0.07199999999999999</v>
@@ -8661,37 +8661,37 @@
         <v>5.04</v>
       </c>
       <c r="M90">
-        <v>14.89048704</v>
+        <v>15.05969712</v>
       </c>
       <c r="N90">
-        <v>-9.850487040000001</v>
+        <v>-10.01969712</v>
       </c>
       <c r="O90">
-        <v>-1.970097408</v>
+        <v>-2.003939424000001</v>
       </c>
       <c r="P90">
-        <v>-7.880389632000001</v>
+        <v>-8.015757696000003</v>
       </c>
       <c r="Q90">
-        <v>-5.700389632000001</v>
+        <v>-5.835757696000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3670080342323995</v>
+        <v>0.396208764617163</v>
       </c>
       <c r="T90">
-        <v>5.416028911561182</v>
+        <v>5.908395176248561</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06769422634009424</v>
+        <v>0.06693361705537408</v>
       </c>
       <c r="W90">
-        <v>0.2198377014290058</v>
+        <v>0.2200170530983428</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3384711317004713</v>
+        <v>0.3346680852768703</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.239398141365413</v>
+        <v>0.241298141365413</v>
       </c>
       <c r="C91">
-        <v>-48.65303782257435</v>
+        <v>-49.51779312510654</v>
       </c>
       <c r="D91">
-        <v>15.14136217742566</v>
+        <v>14.99420687489346</v>
       </c>
       <c r="E91">
-        <v>61.60640000000001</v>
+        <v>62.32400000000001</v>
       </c>
       <c r="F91">
-        <v>63.86640000000001</v>
+        <v>64.584</v>
       </c>
       <c r="G91">
         <v>0.07199999999999999</v>
@@ -8743,37 +8743,37 @@
         <v>5.04</v>
       </c>
       <c r="M91">
-        <v>15.05969712</v>
+        <v>15.2289072</v>
       </c>
       <c r="N91">
-        <v>-10.01969712</v>
+        <v>-10.1889072</v>
       </c>
       <c r="O91">
-        <v>-2.003939424000001</v>
+        <v>-2.037781440000001</v>
       </c>
       <c r="P91">
-        <v>-8.015757696000003</v>
+        <v>-8.151125760000003</v>
       </c>
       <c r="Q91">
-        <v>-5.835757696000003</v>
+        <v>-5.971125760000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.396208764617163</v>
+        <v>0.4312496410788794</v>
       </c>
       <c r="T91">
-        <v>5.908395176248561</v>
+        <v>6.499234693873419</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06693361705537408</v>
+        <v>0.06618991019920326</v>
       </c>
       <c r="W91">
-        <v>0.2200170530983428</v>
+        <v>0.2201924191750279</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3346680852768703</v>
+        <v>0.3309495509960162</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.241298141365413</v>
+        <v>0.243198141365413</v>
       </c>
       <c r="C92">
-        <v>-49.51779312510654</v>
+        <v>-50.37971562411913</v>
       </c>
       <c r="D92">
-        <v>14.99420687489346</v>
+        <v>14.84988437588088</v>
       </c>
       <c r="E92">
-        <v>62.32400000000001</v>
+        <v>63.04160000000001</v>
       </c>
       <c r="F92">
-        <v>64.584</v>
+        <v>65.30160000000001</v>
       </c>
       <c r="G92">
         <v>0.07199999999999999</v>
@@ -8825,37 +8825,37 @@
         <v>5.04</v>
       </c>
       <c r="M92">
-        <v>15.2289072</v>
+        <v>15.39811728</v>
       </c>
       <c r="N92">
-        <v>-10.1889072</v>
+        <v>-10.35811728</v>
       </c>
       <c r="O92">
-        <v>-2.037781440000001</v>
+        <v>-2.071623456000001</v>
       </c>
       <c r="P92">
-        <v>-8.151125760000003</v>
+        <v>-8.286493824000001</v>
       </c>
       <c r="Q92">
-        <v>-5.971125760000003</v>
+        <v>-6.106493824000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4312496410788794</v>
+        <v>0.4740773789765327</v>
       </c>
       <c r="T92">
-        <v>6.499234693873419</v>
+        <v>7.221371882081577</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06618991019920326</v>
+        <v>0.06546254854866256</v>
       </c>
       <c r="W92">
-        <v>0.2201924191750279</v>
+        <v>0.2203639310522254</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3309495509960162</v>
+        <v>0.3273127427433128</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.243198141365413</v>
+        <v>0.245098141365413</v>
       </c>
       <c r="C93">
-        <v>-50.37971562411913</v>
+        <v>-51.23888633883264</v>
       </c>
       <c r="D93">
-        <v>14.84988437588088</v>
+        <v>14.70831366116737</v>
       </c>
       <c r="E93">
-        <v>63.04160000000001</v>
+        <v>63.75920000000001</v>
       </c>
       <c r="F93">
-        <v>65.30160000000001</v>
+        <v>66.01920000000001</v>
       </c>
       <c r="G93">
         <v>0.07199999999999999</v>
@@ -8907,37 +8907,37 @@
         <v>5.04</v>
       </c>
       <c r="M93">
-        <v>15.39811728</v>
+        <v>15.56732736</v>
       </c>
       <c r="N93">
-        <v>-10.35811728</v>
+        <v>-10.52732736</v>
       </c>
       <c r="O93">
-        <v>-2.071623456000001</v>
+        <v>-2.105465472000001</v>
       </c>
       <c r="P93">
-        <v>-8.286493824000001</v>
+        <v>-8.421861888000004</v>
       </c>
       <c r="Q93">
-        <v>-6.106493824000001</v>
+        <v>-6.241861888000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4740773789765327</v>
+        <v>0.5276120513485993</v>
       </c>
       <c r="T93">
-        <v>7.221371882081577</v>
+        <v>8.124043367341777</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06546254854866256</v>
+        <v>0.06475099910791622</v>
       </c>
       <c r="W93">
-        <v>0.2203639310522254</v>
+        <v>0.2205317144103534</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3273127427433128</v>
+        <v>0.3237549955395811</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.245098141365413</v>
+        <v>0.246998141365413</v>
       </c>
       <c r="C94">
-        <v>-51.23888633883264</v>
+        <v>-52.09538322807111</v>
       </c>
       <c r="D94">
-        <v>14.70831366116737</v>
+        <v>14.5694167719289</v>
       </c>
       <c r="E94">
-        <v>63.75920000000001</v>
+        <v>64.4768</v>
       </c>
       <c r="F94">
-        <v>66.01920000000001</v>
+        <v>66.7368</v>
       </c>
       <c r="G94">
         <v>0.07199999999999999</v>
@@ -8989,37 +8989,37 @@
         <v>5.04</v>
       </c>
       <c r="M94">
-        <v>15.56732736</v>
+        <v>15.73653744</v>
       </c>
       <c r="N94">
-        <v>-10.52732736</v>
+        <v>-10.69653744</v>
       </c>
       <c r="O94">
-        <v>-2.105465472000001</v>
+        <v>-2.139307488</v>
       </c>
       <c r="P94">
-        <v>-8.421861888000004</v>
+        <v>-8.557229952</v>
       </c>
       <c r="Q94">
-        <v>-6.241861888000004</v>
+        <v>-6.377229952</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5276120513485993</v>
+        <v>0.5964423443983993</v>
       </c>
       <c r="T94">
-        <v>8.124043367341777</v>
+        <v>9.284620991247746</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06475099910791622</v>
+        <v>0.06405475180568058</v>
       </c>
       <c r="W94">
-        <v>0.2205317144103534</v>
+        <v>0.2206958895242205</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3237549955395811</v>
+        <v>0.3202737590284029</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.246998141365413</v>
+        <v>0.248898141365413</v>
       </c>
       <c r="C95">
-        <v>-52.09538322807111</v>
+        <v>-52.94928133341348</v>
       </c>
       <c r="D95">
-        <v>14.5694167719289</v>
+        <v>14.43311866658652</v>
       </c>
       <c r="E95">
-        <v>64.4768</v>
+        <v>65.1944</v>
       </c>
       <c r="F95">
-        <v>66.7368</v>
+        <v>67.45440000000001</v>
       </c>
       <c r="G95">
         <v>0.07199999999999999</v>
@@ -9071,37 +9071,37 @@
         <v>5.04</v>
       </c>
       <c r="M95">
-        <v>15.73653744</v>
+        <v>15.90574752</v>
       </c>
       <c r="N95">
-        <v>-10.69653744</v>
+        <v>-10.86574752</v>
       </c>
       <c r="O95">
-        <v>-2.139307488</v>
+        <v>-2.173149504000001</v>
       </c>
       <c r="P95">
-        <v>-8.557229952</v>
+        <v>-8.692598016000002</v>
       </c>
       <c r="Q95">
-        <v>-6.377229952</v>
+        <v>-6.512598016000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5964423443983993</v>
+        <v>0.6882160684647993</v>
       </c>
       <c r="T95">
-        <v>9.284620991247746</v>
+        <v>10.83205782312237</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06405475180568058</v>
+        <v>0.06337331827583291</v>
       </c>
       <c r="W95">
-        <v>0.2206958895242205</v>
+        <v>0.2208565715505586</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3202737590284029</v>
+        <v>0.3168665913791645</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.248898141365413</v>
+        <v>0.2507981413654131</v>
       </c>
       <c r="C96">
-        <v>-52.94928133341348</v>
+        <v>-53.80065291438423</v>
       </c>
       <c r="D96">
-        <v>14.43311866658652</v>
+        <v>14.29934708561578</v>
       </c>
       <c r="E96">
-        <v>65.1944</v>
+        <v>65.91200000000001</v>
       </c>
       <c r="F96">
-        <v>67.45440000000001</v>
+        <v>68.17200000000001</v>
       </c>
       <c r="G96">
         <v>0.07199999999999999</v>
@@ -9153,37 +9153,37 @@
         <v>5.04</v>
       </c>
       <c r="M96">
-        <v>15.90574752</v>
+        <v>16.0749576</v>
       </c>
       <c r="N96">
-        <v>-10.86574752</v>
+        <v>-11.03495760000001</v>
       </c>
       <c r="O96">
-        <v>-2.173149504000001</v>
+        <v>-2.206991520000001</v>
       </c>
       <c r="P96">
-        <v>-8.692598016000002</v>
+        <v>-8.827966080000005</v>
       </c>
       <c r="Q96">
-        <v>-6.512598016000002</v>
+        <v>-6.647966080000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6882160684647993</v>
+        <v>0.8166992821577597</v>
       </c>
       <c r="T96">
-        <v>10.83205782312237</v>
+        <v>12.99846938774686</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06337331827583291</v>
+        <v>0.06270623071503466</v>
       </c>
       <c r="W96">
-        <v>0.2208565715505586</v>
+        <v>0.2210138707973948</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3168665913791645</v>
+        <v>0.3135311535751732</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2507981413654131</v>
+        <v>0.252698141365413</v>
       </c>
       <c r="C97">
-        <v>-53.80065291438423</v>
+        <v>-54.64956757619497</v>
       </c>
       <c r="D97">
-        <v>14.29934708561578</v>
+        <v>14.16803242380504</v>
       </c>
       <c r="E97">
-        <v>65.91200000000001</v>
+        <v>66.62960000000001</v>
       </c>
       <c r="F97">
-        <v>68.17200000000001</v>
+        <v>68.88960000000002</v>
       </c>
       <c r="G97">
         <v>0.07199999999999999</v>
@@ -9235,37 +9235,37 @@
         <v>5.04</v>
       </c>
       <c r="M97">
-        <v>16.0749576</v>
+        <v>16.24416768</v>
       </c>
       <c r="N97">
-        <v>-11.03495760000001</v>
+        <v>-11.20416768</v>
       </c>
       <c r="O97">
-        <v>-2.206991520000001</v>
+        <v>-2.240833536000001</v>
       </c>
       <c r="P97">
-        <v>-8.827966080000005</v>
+        <v>-8.963334144000004</v>
       </c>
       <c r="Q97">
-        <v>-6.647966080000005</v>
+        <v>-6.783334144000005</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8166992821577597</v>
+        <v>1.0094241026972</v>
       </c>
       <c r="T97">
-        <v>12.99846938774686</v>
+        <v>16.24808673468358</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06270623071503466</v>
+        <v>0.06205304081175305</v>
       </c>
       <c r="W97">
-        <v>0.2210138707973948</v>
+        <v>0.2211678929765886</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3135311535751732</v>
+        <v>0.3102652040587651</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.252698141365413</v>
+        <v>0.254598141365413</v>
       </c>
       <c r="C98">
-        <v>-54.64956757619495</v>
+        <v>-55.49609239051177</v>
       </c>
       <c r="D98">
-        <v>14.16803242380504</v>
+        <v>14.03910760948824</v>
       </c>
       <c r="E98">
-        <v>66.6296</v>
+        <v>67.3472</v>
       </c>
       <c r="F98">
-        <v>68.8896</v>
+        <v>69.60720000000001</v>
       </c>
       <c r="G98">
         <v>0.07199999999999999</v>
@@ -9317,37 +9317,37 @@
         <v>5.04</v>
       </c>
       <c r="M98">
-        <v>16.24416768</v>
+        <v>16.41337776</v>
       </c>
       <c r="N98">
-        <v>-11.20416768</v>
+        <v>-11.37337776</v>
       </c>
       <c r="O98">
-        <v>-2.240833536</v>
+        <v>-2.274675552000001</v>
       </c>
       <c r="P98">
-        <v>-8.963334144000001</v>
+        <v>-9.098702208000002</v>
       </c>
       <c r="Q98">
-        <v>-6.783334144000001</v>
+        <v>-6.918702208000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.009424102697198</v>
+        <v>1.330632136929597</v>
       </c>
       <c r="T98">
-        <v>16.24808673468353</v>
+        <v>21.66411564624471</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06205304081175306</v>
+        <v>0.06141331874152879</v>
       </c>
       <c r="W98">
-        <v>0.2211678929765886</v>
+        <v>0.2213187394407475</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3102652040587652</v>
+        <v>0.3070665937076439</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.254598141365413</v>
+        <v>0.256498141365413</v>
       </c>
       <c r="C99">
-        <v>-55.49609239051177</v>
+        <v>-56.34029200968813</v>
       </c>
       <c r="D99">
-        <v>14.03910760948824</v>
+        <v>13.91250799031188</v>
       </c>
       <c r="E99">
-        <v>67.3472</v>
+        <v>68.06480000000001</v>
       </c>
       <c r="F99">
-        <v>69.60720000000001</v>
+        <v>70.32480000000001</v>
       </c>
       <c r="G99">
         <v>0.07199999999999999</v>
@@ -9399,37 +9399,37 @@
         <v>5.04</v>
       </c>
       <c r="M99">
-        <v>16.41337776</v>
+        <v>16.58258784</v>
       </c>
       <c r="N99">
-        <v>-11.37337776</v>
+        <v>-11.54258784</v>
       </c>
       <c r="O99">
-        <v>-2.274675552000001</v>
+        <v>-2.308517568000001</v>
       </c>
       <c r="P99">
-        <v>-9.098702208000002</v>
+        <v>-9.234070272000002</v>
       </c>
       <c r="Q99">
-        <v>-6.918702208000003</v>
+        <v>-7.054070272000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.330632136929597</v>
+        <v>1.973048205394395</v>
       </c>
       <c r="T99">
-        <v>21.66411564624471</v>
+        <v>32.49617346936706</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06141331874152879</v>
+        <v>0.06078665222375809</v>
       </c>
       <c r="W99">
-        <v>0.2213187394407475</v>
+        <v>0.2214665074056378</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3070665937076439</v>
+        <v>0.3039332611187904</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.256498141365413</v>
+        <v>0.2583981413654131</v>
       </c>
       <c r="C100">
-        <v>-56.34029200968813</v>
+        <v>-57.18222877487253</v>
       </c>
       <c r="D100">
-        <v>13.91250799031188</v>
+        <v>13.78817122512747</v>
       </c>
       <c r="E100">
-        <v>68.06480000000001</v>
+        <v>68.7824</v>
       </c>
       <c r="F100">
-        <v>70.32480000000001</v>
+        <v>71.0424</v>
       </c>
       <c r="G100">
         <v>0.07199999999999999</v>
@@ -9481,37 +9481,37 @@
         <v>5.04</v>
       </c>
       <c r="M100">
-        <v>16.58258784</v>
+        <v>16.75179792</v>
       </c>
       <c r="N100">
-        <v>-11.54258784</v>
+        <v>-11.71179792</v>
       </c>
       <c r="O100">
-        <v>-2.308517568000001</v>
+        <v>-2.342359584</v>
       </c>
       <c r="P100">
-        <v>-9.234070272000002</v>
+        <v>-9.369438336000002</v>
       </c>
       <c r="Q100">
-        <v>-7.054070272000002</v>
+        <v>-7.189438336000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.973048205394395</v>
+        <v>3.90029641078879</v>
       </c>
       <c r="T100">
-        <v>32.49617346936706</v>
+        <v>64.99234693873413</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06078665222375809</v>
+        <v>0.06017264563563932</v>
       </c>
       <c r="W100">
-        <v>0.2214665074056378</v>
+        <v>0.2216112901591163</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3039332611187904</v>
+        <v>0.3008632281781966</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2583981413654131</v>
-      </c>
-      <c r="C101">
-        <v>-57.18222877487253</v>
-      </c>
-      <c r="D101">
-        <v>13.78817122512747</v>
-      </c>
-      <c r="E101">
-        <v>68.7824</v>
-      </c>
-      <c r="F101">
-        <v>71.0424</v>
-      </c>
-      <c r="G101">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="H101">
-        <v>69.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.22</v>
-      </c>
-      <c r="K101">
-        <v>2.18</v>
-      </c>
-      <c r="L101">
-        <v>5.04</v>
-      </c>
-      <c r="M101">
-        <v>16.75179792</v>
-      </c>
-      <c r="N101">
-        <v>-11.71179792</v>
-      </c>
-      <c r="O101">
-        <v>-2.342359584</v>
-      </c>
-      <c r="P101">
-        <v>-9.369438336000002</v>
-      </c>
-      <c r="Q101">
-        <v>-7.189438336000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.90029641078879</v>
-      </c>
-      <c r="T101">
-        <v>64.99234693873413</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06017264563563932</v>
-      </c>
-      <c r="W101">
-        <v>0.2216112901591163</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3008632281781966</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
